--- a/handouts/chapter_1_4_handout.xlsx
+++ b/handouts/chapter_1_4_handout.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RussellStuff\Time series personal work\timeseries\handouts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\craigaj\Documents\GitHub\timeseries\handouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D83CA26-CEE7-4228-9F01-109894F175A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC944B35-E5FD-4906-9307-671D58DB5C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
+    <workbookView xWindow="-11055" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
   </bookViews>
   <sheets>
     <sheet name="Workbook" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
     <author>Tyson Brost</author>
   </authors>
   <commentList>
-    <comment ref="N70" authorId="0" shapeId="0" xr:uid="{03604686-DD39-44B3-8C52-9AB952A455A0}">
+    <comment ref="N72" authorId="0" shapeId="0" xr:uid="{03604686-DD39-44B3-8C52-9AB952A455A0}">
       <text>
         <r>
           <rPr>
@@ -54,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A72" authorId="0" shapeId="0" xr:uid="{B9005AA8-9127-4531-8981-BB5C15A6BF94}">
+    <comment ref="A74" authorId="0" shapeId="0" xr:uid="{B9005AA8-9127-4531-8981-BB5C15A6BF94}">
       <text>
         <r>
           <rPr>
@@ -67,7 +67,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A73" authorId="0" shapeId="0" xr:uid="{7BCDF08E-591D-4779-914C-43B84F576306}">
+    <comment ref="A75" authorId="0" shapeId="0" xr:uid="{7BCDF08E-591D-4779-914C-43B84F576306}">
       <text>
         <r>
           <rPr>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="83">
   <si>
     <t>Month</t>
   </si>
@@ -320,9 +320,6 @@
     <t>Dec</t>
   </si>
   <si>
-    <t>Mean</t>
-  </si>
-  <si>
     <t>Overall
 Mean</t>
   </si>
@@ -330,14 +327,17 @@
     <t>NA</t>
   </si>
   <si>
-    <t>Table 3: Computation of        the Random Component, and the Seasonally Adjusted Time Series</t>
-  </si>
-  <si>
     <t>Table 2: Computation of</t>
   </si>
   <si>
     <t>Table 1: Computation of the 
 Centered Moving Average,      , and the Estimated Monthly Additive Effect,</t>
+  </si>
+  <si>
+    <t>Table 3: Computation of        the Random Component and the Seasonally Adjusted Time Series</t>
+  </si>
+  <si>
+    <t>Mean,</t>
   </si>
 </sst>
 </file>
@@ -405,7 +405,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="3" tint="0.89999084444715716"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -591,24 +591,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -675,7 +667,30 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -699,7 +714,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>295434</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>205613</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="196079" cy="221214"/>
@@ -749,10 +764,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -847,7 +859,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>295434</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>137033</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="187167" cy="221214"/>
@@ -897,15 +909,12 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̂"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -988,7 +997,7 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>341154</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>137033</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="120161" cy="221214"/>
@@ -1038,15 +1047,12 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̂"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -1129,7 +1135,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>320040</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>110490</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="120161" cy="221214"/>
@@ -1179,15 +1185,12 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̅"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -1270,7 +1273,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>569754</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>205613</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="196079" cy="221214"/>
@@ -1320,10 +1323,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1418,7 +1418,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>112</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>3810</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="65" cy="172227"/>
@@ -1523,10 +1523,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1671,15 +1668,12 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̂"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -1812,15 +1806,12 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̂"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -1903,7 +1894,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>3810</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="65" cy="172227"/>
@@ -1957,13 +1948,13 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>251460</xdr:colOff>
+      <xdr:colOff>387985</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>255270</xdr:rowOff>
+      <xdr:rowOff>163195</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="320040" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="TextBox 14">
@@ -1977,7 +1968,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="251460" y="14077950"/>
+              <a:off x="387985" y="13860145"/>
               <a:ext cx="320040" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2008,10 +1999,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -2025,7 +2013,7 @@
                           <m:accPr>
                             <m:chr m:val="̅"/>
                             <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1400" i="1">
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -2057,7 +2045,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="TextBox 14">
@@ -2071,7 +2059,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="251460" y="14077950"/>
+              <a:off x="387985" y="13860145"/>
               <a:ext cx="320040" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2118,7 +2106,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>3810</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="180819" cy="231923"/>
@@ -2168,10 +2156,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̅"/>
@@ -2195,7 +2180,7 @@
                               <m:accPr>
                                 <m:chr m:val="̂"/>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1400" i="1">
+                                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
@@ -2295,13 +2280,13 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>449580</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>152399</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="180819" cy="250903"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <xdr:ext cx="379575" cy="250903"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="TextBox 16">
@@ -2315,8 +2300,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9928860" y="19777710"/>
-              <a:ext cx="180819" cy="250903"/>
+              <a:off x="10001249" y="14458950"/>
+              <a:ext cx="379575" cy="250903"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2338,76 +2323,74 @@
             </a:fontRef>
           </xdr:style>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
               <a:spAutoFit/>
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr/>
               <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:acc>
-                      <m:accPr>
-                        <m:chr m:val="̿"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:accPr>
-                      <m:e>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1400" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:acc>
-                              <m:accPr>
-                                <m:chr m:val="̂"/>
-                                <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1400" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                </m:ctrlPr>
-                              </m:accPr>
-                              <m:e>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑠</m:t>
-                                </m:r>
-                              </m:e>
-                            </m:acc>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑡</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:e>
-                    </m:acc>
-                  </m:oMath>
-                </m:oMathPara>
+                <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:acc>
+                    <m:accPr>
+                      <m:chr m:val="̿"/>
+                      <m:ctrlPr>
+                        <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
+                      </m:ctrlPr>
+                    </m:accPr>
+                    <m:e>
+                      <m:sSub>
+                        <m:sSubPr>
+                          <m:ctrlPr>
+                            <a:rPr lang="en-US" sz="1400" i="1">
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            </a:rPr>
+                          </m:ctrlPr>
+                        </m:sSubPr>
+                        <m:e>
+                          <m:acc>
+                            <m:accPr>
+                              <m:chr m:val="̂"/>
+                              <m:ctrlPr>
+                                <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                </a:rPr>
+                              </m:ctrlPr>
+                            </m:accPr>
+                            <m:e>
+                              <m:r>
+                                <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                </a:rPr>
+                                <m:t>𝑠</m:t>
+                              </m:r>
+                            </m:e>
+                          </m:acc>
+                        </m:e>
+                        <m:sub>
+                          <m:r>
+                            <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            </a:rPr>
+                            <m:t>𝑡</m:t>
+                          </m:r>
+                        </m:sub>
+                      </m:sSub>
+                    </m:e>
+                  </m:acc>
+                </m:oMath>
               </a14:m>
-              <a:endParaRPr lang="en-US" sz="1400"/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1400"/>
+                <a:t>=</a:t>
+              </a:r>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="TextBox 16">
@@ -2421,8 +2404,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9928860" y="19777710"/>
-              <a:ext cx="180819" cy="250903"/>
+              <a:off x="10001249" y="14458950"/>
+              <a:ext cx="379575" cy="250903"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2444,7 +2427,7 @@
             </a:fontRef>
           </xdr:style>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
               <a:spAutoFit/>
             </a:bodyPr>
             <a:lstStyle/>
@@ -2462,7 +2445,10 @@
                 </a:rPr>
                 <a:t>𝑠 ̂_𝑡 ) ̿</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="1400"/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1400"/>
+                <a:t>=</a:t>
+              </a:r>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2473,13 +2459,13 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>102870</xdr:rowOff>
+      <xdr:colOff>202565</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>77470</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="320040" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="18" name="TextBox 17">
@@ -2493,7 +2479,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1851660" y="14801850"/>
+              <a:off x="1878965" y="15546070"/>
               <a:ext cx="320040" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2524,37 +2510,22 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
-                        <m:acc>
-                          <m:accPr>
-                            <m:chr m:val="̅"/>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1400" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:accPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑠</m:t>
-                            </m:r>
-                          </m:e>
-                        </m:acc>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑧</m:t>
+                        </m:r>
                       </m:e>
                       <m:sub>
                         <m:r>
@@ -2573,7 +2544,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="18" name="TextBox 17">
@@ -2587,7 +2558,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1851660" y="14801850"/>
+              <a:off x="1878965" y="15546070"/>
               <a:ext cx="320040" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2620,7 +2591,7 @@
                 <a:rPr lang="en-US" sz="1400" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>𝑠 ̅_𝑡</a:t>
+                <a:t>𝑧_𝑡</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1400"/>
             </a:p>
@@ -2634,7 +2605,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>891540</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>118110</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="320040" cy="221214"/>
@@ -2684,10 +2655,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -2701,7 +2669,7 @@
                           <m:accPr>
                             <m:chr m:val="̅"/>
                             <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1400" i="1">
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -2794,7 +2762,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>243840</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:row>102</xdr:row>
       <xdr:rowOff>179070</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="70147" cy="173766"/>
@@ -2844,10 +2812,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:r>
                       <a:rPr lang="en-US" sz="1100" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -2878,786 +2843,6 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="243840" y="19541490"/>
-              <a:ext cx="70147" cy="173766"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>⋮</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>358140</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>179070</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="21" name="TextBox 20">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5155B11E-5613-4C5A-8607-612173AF2460}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="967740" y="19541490"/>
-              <a:ext cx="70147" cy="173766"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>⋮</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="21" name="TextBox 20">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5155B11E-5613-4C5A-8607-612173AF2460}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="967740" y="19541490"/>
-              <a:ext cx="70147" cy="173766"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>⋮</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>388620</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>3810</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="22" name="TextBox 21">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FBBA55C8-9E10-4313-8376-EEE928A976BB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="1767840" y="19549110"/>
-              <a:ext cx="70147" cy="173766"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>⋮</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="22" name="TextBox 21">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FBBA55C8-9E10-4313-8376-EEE928A976BB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="1767840" y="19549110"/>
-              <a:ext cx="70147" cy="173766"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>⋮</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>350520</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>3810</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="23" name="TextBox 22">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FCC7F7B-74F2-42C2-8A24-0BEFB19A9685}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2567940" y="19549110"/>
-              <a:ext cx="70147" cy="173766"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>⋮</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="23" name="TextBox 22">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FCC7F7B-74F2-42C2-8A24-0BEFB19A9685}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2567940" y="19549110"/>
-              <a:ext cx="70147" cy="173766"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>⋮</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>358140</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>179070</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="24" name="TextBox 23">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC25D056-899E-4DCE-AA9F-30CAFBEB4D2D}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3345180" y="19541490"/>
-              <a:ext cx="70147" cy="173766"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>⋮</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="24" name="TextBox 23">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC25D056-899E-4DCE-AA9F-30CAFBEB4D2D}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3345180" y="19541490"/>
-              <a:ext cx="70147" cy="173766"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>⋮</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>350520</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>3810</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="25" name="TextBox 24">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9A0D687-1973-464B-BFC4-F10BB460D52B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4107180" y="19549110"/>
-              <a:ext cx="70147" cy="173766"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>⋮</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="25" name="TextBox 24">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9A0D687-1973-464B-BFC4-F10BB460D52B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4107180" y="19549110"/>
-              <a:ext cx="70147" cy="173766"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>⋮</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>601980</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>3810</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="70147" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="26" name="TextBox 25">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8892574A-7E4B-4608-97D5-6D7620B37EA2}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5128260" y="19549110"/>
-              <a:ext cx="70147" cy="173766"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>⋮</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="26" name="TextBox 25">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8892574A-7E4B-4608-97D5-6D7620B37EA2}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5128260" y="19549110"/>
               <a:ext cx="70147" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3754,15 +2939,12 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̂"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -3895,15 +3077,12 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̂"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -3973,6 +3152,163 @@
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝑠 ̂</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" sz="1400"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="320040" cy="221214"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="8" name="TextBox 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F45778D0-E675-4554-B0C0-B79E5020600B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5781675" y="13011150"/>
+              <a:ext cx="320040" cy="221214"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1400" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:acc>
+                          <m:accPr>
+                            <m:chr m:val="̅"/>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:accPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑠</m:t>
+                            </m:r>
+                          </m:e>
+                        </m:acc>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" sz="1400"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="8" name="TextBox 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F45778D0-E675-4554-B0C0-B79E5020600B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5781675" y="13011150"/>
+              <a:ext cx="320040" cy="221214"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1400" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑠 ̅_𝑡</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1400"/>
             </a:p>
@@ -4302,7 +3638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ABFF2E6-1E13-48EF-9BE3-D6C90C46BEC8}">
-  <dimension ref="A1:N113"/>
+  <dimension ref="A1:N139"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
@@ -4313,1696 +3649,1699 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="45.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="32"/>
+    </row>
+    <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="11"/>
+      <c r="D2" s="20"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="33">
+        <v>3034</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="33">
+        <v>2748</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="33">
+        <v>3164</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="33">
+        <v>3238</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="33">
+        <v>3416</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="33">
+        <v>3492</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="33">
+        <v>3730</v>
+      </c>
+      <c r="C9" s="35">
+        <v>3351.5833333333335</v>
+      </c>
+      <c r="D9" s="37">
+        <f>IFERROR(B9-C9, "NA")</f>
+        <v>378.41666666666652</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="33">
+        <v>3409</v>
+      </c>
+      <c r="C10" s="35">
+        <v>3350</v>
+      </c>
+      <c r="D10" s="36"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="33">
+        <v>3572</v>
+      </c>
+      <c r="C11" s="35">
+        <v>3343.2083333333335</v>
+      </c>
+      <c r="D11" s="36"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="33">
+        <v>3629</v>
+      </c>
+      <c r="C12" s="35">
+        <v>3326.2083333333335</v>
+      </c>
+      <c r="D12" s="36"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="33">
+        <v>3408</v>
+      </c>
+      <c r="C13" s="35">
+        <v>3316.5416666666665</v>
+      </c>
+      <c r="D13" s="36"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="33">
+        <v>3391</v>
+      </c>
+      <c r="C14" s="35">
+        <v>3318.5833333333335</v>
+      </c>
+      <c r="D14" s="36"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="33">
+        <v>3010</v>
+      </c>
+      <c r="C15" s="35">
+        <v>3312.0833333333335</v>
+      </c>
+      <c r="D15" s="36"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="33">
+        <v>2734</v>
+      </c>
+      <c r="C16" s="35">
+        <v>3308.0416666666665</v>
+      </c>
+      <c r="D16" s="36"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="33">
+        <v>3015</v>
+      </c>
+      <c r="C17" s="35">
+        <v>3311.7083333333335</v>
+      </c>
+      <c r="D17" s="36"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="33">
+        <v>2979</v>
+      </c>
+      <c r="C18" s="35">
+        <v>3313.1666666666665</v>
+      </c>
+      <c r="D18" s="36"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="33">
+        <v>3443</v>
+      </c>
+      <c r="C19" s="35">
+        <v>3307.75</v>
+      </c>
+      <c r="D19" s="36"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="33">
+        <v>3514</v>
+      </c>
+      <c r="C20" s="35">
+        <v>3292.4166666666665</v>
+      </c>
+      <c r="D20" s="36"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="33">
+        <v>3552</v>
+      </c>
+      <c r="C21" s="35">
+        <v>3281.0833333333335</v>
+      </c>
+      <c r="D21" s="36"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="33">
+        <v>3490</v>
+      </c>
+      <c r="C22" s="35">
+        <v>3270.2083333333335</v>
+      </c>
+      <c r="D22" s="36"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="33">
+        <v>3579</v>
+      </c>
+      <c r="C23" s="35">
+        <v>3259.4583333333335</v>
+      </c>
+      <c r="D23" s="36"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="33">
+        <v>3657</v>
+      </c>
+      <c r="C24" s="35">
+        <v>3261.1666666666665</v>
+      </c>
+      <c r="D24" s="36"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="33">
+        <v>3250</v>
+      </c>
+      <c r="C25" s="35">
+        <v>3264.25</v>
+      </c>
+      <c r="D25" s="36"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="33">
+        <v>3181</v>
+      </c>
+      <c r="C26" s="35">
+        <v>3260.4583333333335</v>
+      </c>
+      <c r="D26" s="36"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="33">
+        <v>2948</v>
+      </c>
+      <c r="C27" s="35">
+        <v>3256.7083333333335</v>
+      </c>
+      <c r="D27" s="36"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="33">
+        <v>2535</v>
+      </c>
+      <c r="C28" s="35">
+        <v>3262.125</v>
+      </c>
+      <c r="D28" s="36"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="33">
+        <v>2956</v>
+      </c>
+      <c r="C29" s="35">
+        <v>3267.0833333333335</v>
+      </c>
+      <c r="D29" s="36"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="33">
+        <v>3079</v>
+      </c>
+      <c r="C30" s="35">
+        <v>3259.2916666666665</v>
+      </c>
+      <c r="D30" s="36"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="33">
+        <v>3417</v>
+      </c>
+      <c r="C31" s="35">
+        <v>3254</v>
+      </c>
+      <c r="D31" s="36"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="33">
+        <v>3449</v>
+      </c>
+      <c r="C32" s="35">
+        <v>3256.9583333333335</v>
+      </c>
+      <c r="D32" s="36"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="33">
+        <v>3527</v>
+      </c>
+      <c r="C33" s="35">
+        <v>3256.7083333333335</v>
+      </c>
+      <c r="D33" s="36"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="33">
+        <v>3645</v>
+      </c>
+      <c r="C34" s="35">
+        <v>3269</v>
+      </c>
+      <c r="D34" s="36"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="33">
+        <v>3543</v>
+      </c>
+      <c r="C35" s="35">
+        <v>3279.0833333333335</v>
+      </c>
+      <c r="D35" s="36"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="33">
+        <v>3506</v>
+      </c>
+      <c r="C36" s="35">
+        <v>3252.8333333333335</v>
+      </c>
+      <c r="D36" s="36"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="33">
+        <v>3274</v>
+      </c>
+      <c r="C37" s="35">
+        <v>3228.0416666666665</v>
+      </c>
+      <c r="D37" s="36"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="33">
+        <v>3228</v>
+      </c>
+      <c r="C38" s="35">
+        <v>3248.2083333333335</v>
+      </c>
+      <c r="D38" s="36"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="33">
+        <v>2895</v>
+      </c>
+      <c r="C39" s="35">
+        <v>3294.2916666666665</v>
+      </c>
+      <c r="D39" s="36"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="33">
+        <v>2883</v>
+      </c>
+      <c r="C40" s="35">
+        <v>3340.3333333333335</v>
+      </c>
+      <c r="D40" s="36"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="33">
+        <v>2850</v>
+      </c>
+      <c r="C41" s="35">
+        <v>3384.6666666666665</v>
+      </c>
+      <c r="D41" s="36"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="33">
+        <v>2555</v>
+      </c>
+      <c r="C42" s="35">
+        <v>3433.5416666666665</v>
+      </c>
+      <c r="D42" s="36"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="33">
+        <v>3346</v>
+      </c>
+      <c r="C43" s="35">
+        <v>3481.2916666666665</v>
+      </c>
+      <c r="D43" s="36"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="33">
+        <v>4004</v>
+      </c>
+      <c r="C44" s="35">
+        <v>3514.8333333333335</v>
+      </c>
+      <c r="D44" s="36"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" s="33">
+        <v>4078</v>
+      </c>
+      <c r="C45" s="35">
+        <v>3549.875</v>
+      </c>
+      <c r="D45" s="36"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="33">
+        <v>4199</v>
+      </c>
+      <c r="C46" s="35">
+        <v>3567.7083333333335</v>
+      </c>
+      <c r="D46" s="36"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" s="33">
+        <v>4053</v>
+      </c>
+      <c r="C47" s="35">
+        <v>3590.6666666666665</v>
+      </c>
+      <c r="D47" s="36"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" s="33">
+        <v>4169</v>
+      </c>
+      <c r="C48" s="35">
+        <v>3672.125</v>
+      </c>
+      <c r="D48" s="36"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" s="33">
+        <v>3757</v>
+      </c>
+      <c r="C49" s="35">
+        <v>3758.1666666666665</v>
+      </c>
+      <c r="D49" s="36"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" s="33">
+        <v>3550</v>
+      </c>
+      <c r="C50" s="35">
+        <v>3793.7916666666665</v>
+      </c>
+      <c r="D50" s="36"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" s="33">
+        <v>3414</v>
+      </c>
+      <c r="C51" s="35">
+        <v>3804.8333333333335</v>
+      </c>
+      <c r="D51" s="36"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" s="33">
+        <v>2792</v>
+      </c>
+      <c r="C52" s="35">
+        <v>3816.625</v>
+      </c>
+      <c r="D52" s="36"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" s="33">
+        <v>3492</v>
+      </c>
+      <c r="C53" s="35">
+        <v>3830.9583333333335</v>
+      </c>
+      <c r="D53" s="36"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" s="33">
+        <v>3868</v>
+      </c>
+      <c r="C54" s="35">
+        <v>3853.2916666666665</v>
+      </c>
+      <c r="D54" s="36"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" s="33">
+        <v>4098</v>
+      </c>
+      <c r="C55" s="35">
+        <v>3875.5</v>
+      </c>
+      <c r="D55" s="36"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" s="33">
+        <v>4107</v>
+      </c>
+      <c r="C56" s="35">
+        <v>3899.8333333333335</v>
+      </c>
+      <c r="D56" s="36"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57" s="33">
+        <v>4240</v>
+      </c>
+      <c r="C57" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D57" s="36"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58" s="33">
+        <v>4320</v>
+      </c>
+      <c r="C58" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D58" s="36"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B59" s="33">
+        <v>4276</v>
+      </c>
+      <c r="C59" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D59" s="36"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B60" s="33">
+        <v>4482</v>
+      </c>
+      <c r="C60" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D60" s="36"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B61" s="33">
+        <v>3977</v>
+      </c>
+      <c r="C61" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D61" s="36"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B62" s="38">
+        <v>3914</v>
+      </c>
+      <c r="C62" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="D62" s="36"/>
+    </row>
+    <row r="66" spans="1:14" ht="34.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B66" s="29"/>
+      <c r="C66" s="29"/>
+      <c r="D66" s="29"/>
+      <c r="E66" s="29"/>
+      <c r="F66" s="29"/>
+      <c r="G66" s="29"/>
+      <c r="H66" s="29"/>
+      <c r="I66" s="29"/>
+      <c r="J66" s="29"/>
+      <c r="K66" s="29"/>
+      <c r="L66" s="29"/>
+      <c r="M66" s="29"/>
+      <c r="N66" s="2"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A67" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B67" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E67" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F67" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="G67" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="H67" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="I67" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="J67" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M67" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="N67" s="5"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A68" s="22">
+        <v>2017</v>
+      </c>
+      <c r="B68" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="C68" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D68" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="E68" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="F68" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="G68" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="H68" s="36"/>
+      <c r="I68" s="36"/>
+      <c r="J68" s="36"/>
+      <c r="K68" s="36"/>
+      <c r="L68" s="36"/>
+      <c r="M68" s="36"/>
+      <c r="N68" s="6"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A69" s="22">
+        <v>2018</v>
+      </c>
+      <c r="B69" s="36"/>
+      <c r="C69" s="36"/>
+      <c r="D69" s="35">
+        <v>-296.70833333333348</v>
+      </c>
+      <c r="E69" s="35">
+        <v>-334.16666666666652</v>
+      </c>
+      <c r="F69" s="35">
+        <v>135.25</v>
+      </c>
+      <c r="G69" s="35">
+        <v>221.58333333333348</v>
+      </c>
+      <c r="H69" s="35">
+        <v>270.91666666666652</v>
+      </c>
+      <c r="I69" s="35">
+        <v>219.79166666666652</v>
+      </c>
+      <c r="J69" s="35">
+        <v>319.54166666666652</v>
+      </c>
+      <c r="K69" s="35">
+        <v>395.83333333333348</v>
+      </c>
+      <c r="L69" s="35">
+        <v>-14.25</v>
+      </c>
+      <c r="M69" s="37">
+        <v>-79.458333333333485</v>
+      </c>
+      <c r="N69" s="6"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A70" s="22">
+        <v>2019</v>
+      </c>
+      <c r="B70" s="35">
+        <v>-308.70833333333348</v>
+      </c>
+      <c r="C70" s="35">
+        <v>-727.125</v>
+      </c>
+      <c r="D70" s="35">
+        <v>-311.08333333333348</v>
+      </c>
+      <c r="E70" s="35">
+        <v>-180.29166666666652</v>
+      </c>
+      <c r="F70" s="35">
+        <v>163</v>
+      </c>
+      <c r="G70" s="35">
+        <v>192.04166666666652</v>
+      </c>
+      <c r="H70" s="35">
+        <v>270.29166666666652</v>
+      </c>
+      <c r="I70" s="35">
+        <v>376</v>
+      </c>
+      <c r="J70" s="35">
+        <v>263.91666666666652</v>
+      </c>
+      <c r="K70" s="35">
+        <v>253.16666666666652</v>
+      </c>
+      <c r="L70" s="35">
+        <v>45.958333333333485</v>
+      </c>
+      <c r="M70" s="37">
+        <v>-20.208333333333485</v>
+      </c>
+      <c r="N70" s="6"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A71" s="22">
+        <v>2020</v>
+      </c>
+      <c r="B71" s="35">
+        <v>-399.29166666666652</v>
+      </c>
+      <c r="C71" s="35">
+        <v>-457.33333333333348</v>
+      </c>
+      <c r="D71" s="35">
+        <v>-534.66666666666652</v>
+      </c>
+      <c r="E71" s="35">
+        <v>-878.54166666666652</v>
+      </c>
+      <c r="F71" s="35">
+        <v>-135.29166666666652</v>
+      </c>
+      <c r="G71" s="35">
+        <v>489.16666666666652</v>
+      </c>
+      <c r="H71" s="35">
+        <v>528.125</v>
+      </c>
+      <c r="I71" s="35">
+        <v>631.29166666666652</v>
+      </c>
+      <c r="J71" s="35">
+        <v>462.33333333333348</v>
+      </c>
+      <c r="K71" s="35">
+        <v>496.875</v>
+      </c>
+      <c r="L71" s="35">
+        <v>-1.1666666666665151</v>
+      </c>
+      <c r="M71" s="37">
+        <v>-243.79166666666652</v>
+      </c>
+      <c r="N71" s="23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A72" s="22">
+        <v>2021</v>
+      </c>
+      <c r="B72" s="35">
+        <v>-390.83333333333348</v>
+      </c>
+      <c r="C72" s="35">
+        <v>-1024.625</v>
+      </c>
+      <c r="D72" s="35">
+        <v>-338.95833333333348</v>
+      </c>
+      <c r="E72" s="35">
+        <v>14.708333333333485</v>
+      </c>
+      <c r="F72" s="35">
+        <v>222.5</v>
+      </c>
+      <c r="G72" s="35">
+        <v>207.16666666666652</v>
+      </c>
+      <c r="H72" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="I72" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="J72" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="K72" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="L72" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="M72" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="N72" s="24"/>
+    </row>
+    <row r="73" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="38"/>
-    </row>
-    <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+      <c r="B73" s="35">
+        <v>-350.22916666666674</v>
+      </c>
+      <c r="C73" s="35">
+        <v>-695.78125</v>
+      </c>
+      <c r="D73" s="35">
+        <v>-370.35416666666674</v>
+      </c>
+      <c r="E73" s="36"/>
+      <c r="F73" s="36"/>
+      <c r="G73" s="36"/>
+      <c r="H73" s="36"/>
+      <c r="I73" s="36"/>
+      <c r="J73" s="36"/>
+      <c r="K73" s="36"/>
+      <c r="L73" s="36"/>
+      <c r="M73" s="36"/>
+      <c r="N73" s="7">
+        <v>-5.0060763888889142</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="19.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="19"/>
+      <c r="B74" s="40">
+        <v>-345.22309027777783</v>
+      </c>
+      <c r="C74" s="36"/>
+      <c r="D74" s="36"/>
+      <c r="E74" s="36"/>
+      <c r="F74" s="36"/>
+      <c r="G74" s="36"/>
+      <c r="H74" s="36"/>
+      <c r="I74" s="36"/>
+      <c r="J74" s="36"/>
+      <c r="K74" s="36"/>
+      <c r="L74" s="36"/>
+      <c r="M74" s="36"/>
+      <c r="N74" s="8"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35"/>
+    <row r="78" spans="1:14" ht="43.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A78" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B78" s="26"/>
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="27"/>
+    </row>
+    <row r="79" spans="1:14" ht="37.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B79" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="26"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="C79" s="14"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="14"/>
+      <c r="F79" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G79" s="15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A80" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="B80" s="33">
+        <f>B3</f>
         <v>3034</v>
       </c>
-      <c r="C3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="C80" s="33" t="str">
+        <f t="shared" ref="C80:D80" si="0">C3</f>
+        <v>NA</v>
+      </c>
+      <c r="D80" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>NA</v>
+      </c>
+      <c r="E80" s="36"/>
+      <c r="F80" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="G80" s="36"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="B81" s="33">
+        <f t="shared" ref="B81:D96" si="1">B4</f>
         <v>2748</v>
       </c>
-      <c r="C4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="C81" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>NA</v>
+      </c>
+      <c r="D81" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>NA</v>
+      </c>
+      <c r="E81" s="36"/>
+      <c r="F81" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="G81" s="36"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A82" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
+      <c r="B82" s="33">
+        <f t="shared" si="1"/>
         <v>3164</v>
       </c>
-      <c r="C5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+      <c r="C82" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>NA</v>
+      </c>
+      <c r="D82" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>NA</v>
+      </c>
+      <c r="E82" s="36"/>
+      <c r="F82" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="G82" s="36"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A83" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
+      <c r="B83" s="33">
+        <f t="shared" si="1"/>
         <v>3238</v>
       </c>
-      <c r="C6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+      <c r="C83" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>NA</v>
+      </c>
+      <c r="D83" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>NA</v>
+      </c>
+      <c r="E83" s="36"/>
+      <c r="F83" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="G83" s="36"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A84" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7">
+      <c r="B84" s="33">
+        <f t="shared" si="1"/>
         <v>3416</v>
       </c>
-      <c r="C7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
+      <c r="C84" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>NA</v>
+      </c>
+      <c r="D84" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>NA</v>
+      </c>
+      <c r="E84" s="36"/>
+      <c r="F84" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="G84" s="36"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A85" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B8">
+      <c r="B85" s="33">
+        <f t="shared" si="1"/>
         <v>3492</v>
       </c>
-      <c r="C8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
+      <c r="C85" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>NA</v>
+      </c>
+      <c r="D85" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>NA</v>
+      </c>
+      <c r="E85" s="36"/>
+      <c r="F85" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="G85" s="36"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A86" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B9">
+      <c r="B86" s="33">
+        <f t="shared" si="1"/>
         <v>3730</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C86" s="35">
+        <f t="shared" si="1"/>
         <v>3351.5833333333335</v>
       </c>
-      <c r="D9" s="39"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
+      <c r="D86" s="37">
+        <f t="shared" si="1"/>
+        <v>378.41666666666652</v>
+      </c>
+      <c r="E86" s="36"/>
+      <c r="F86" s="36"/>
+      <c r="G86" s="36"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A87" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B10">
+      <c r="B87" s="33">
+        <f t="shared" si="1"/>
         <v>3409</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C87" s="35">
+        <f t="shared" si="1"/>
         <v>3350</v>
       </c>
-      <c r="D10" s="39"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
+      <c r="D87" s="37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E87" s="36"/>
+      <c r="F87" s="36"/>
+      <c r="G87" s="36"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A88" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B11">
+      <c r="B88" s="33">
+        <f t="shared" si="1"/>
         <v>3572</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C88" s="35">
+        <f t="shared" si="1"/>
         <v>3343.2083333333335</v>
       </c>
-      <c r="D11" s="39"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
+      <c r="D88" s="37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E88" s="36"/>
+      <c r="F88" s="36"/>
+      <c r="G88" s="36"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A89" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B12">
+      <c r="B89" s="33">
+        <f t="shared" si="1"/>
         <v>3629</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C89" s="35">
+        <f t="shared" si="1"/>
         <v>3326.2083333333335</v>
       </c>
-      <c r="D12" s="39"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
+      <c r="D89" s="37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E89" s="36"/>
+      <c r="F89" s="36"/>
+      <c r="G89" s="36"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A90" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B13">
+      <c r="B90" s="33">
+        <f t="shared" si="1"/>
         <v>3408</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C90" s="35">
+        <f t="shared" si="1"/>
         <v>3316.5416666666665</v>
       </c>
-      <c r="D13" s="39"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
+      <c r="D90" s="37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E90" s="36"/>
+      <c r="F90" s="36"/>
+      <c r="G90" s="36"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A91" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B14">
+      <c r="B91" s="33">
+        <f t="shared" si="1"/>
         <v>3391</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C91" s="35">
+        <f t="shared" si="1"/>
         <v>3318.5833333333335</v>
       </c>
-      <c r="D14" s="39"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
+      <c r="D91" s="37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E91" s="36"/>
+      <c r="F91" s="36"/>
+      <c r="G91" s="36"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A92" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B15">
+      <c r="B92" s="33">
+        <f t="shared" si="1"/>
         <v>3010</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C92" s="35">
+        <f t="shared" si="1"/>
         <v>3312.0833333333335</v>
       </c>
-      <c r="D15" s="39"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
+      <c r="D92" s="37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E92" s="36"/>
+      <c r="F92" s="36"/>
+      <c r="G92" s="36"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A93" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B16">
+      <c r="B93" s="33">
+        <f t="shared" si="1"/>
         <v>2734</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C93" s="35">
+        <f t="shared" si="1"/>
         <v>3308.0416666666665</v>
       </c>
-      <c r="D16" s="39"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
+      <c r="D93" s="37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E93" s="36"/>
+      <c r="F93" s="36"/>
+      <c r="G93" s="36"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A94" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B17">
+      <c r="B94" s="33">
+        <f t="shared" si="1"/>
         <v>3015</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C94" s="35">
+        <f t="shared" si="1"/>
         <v>3311.7083333333335</v>
       </c>
-      <c r="D17" s="8">
-        <v>-296.70833333333348</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
+      <c r="D94" s="37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E94" s="36"/>
+      <c r="F94" s="36"/>
+      <c r="G94" s="36"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A95" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B18">
+      <c r="B95" s="33">
+        <f t="shared" si="1"/>
         <v>2979</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C95" s="35">
+        <f t="shared" si="1"/>
         <v>3313.1666666666665</v>
       </c>
-      <c r="D18" s="8">
-        <v>-334.16666666666652</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
+      <c r="D95" s="37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E95" s="36"/>
+      <c r="F95" s="36"/>
+      <c r="G95" s="36"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A96" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B19">
+      <c r="B96" s="33">
+        <f t="shared" si="1"/>
         <v>3443</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C96" s="35">
+        <f t="shared" si="1"/>
         <v>3307.75</v>
       </c>
-      <c r="D19" s="8">
-        <v>135.25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
+      <c r="D96" s="37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E96" s="36"/>
+      <c r="F96" s="36"/>
+      <c r="G96" s="36"/>
+      <c r="H96" s="1"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A97" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B20">
+      <c r="B97" s="33">
+        <f t="shared" ref="B97:D112" si="2">B20</f>
         <v>3514</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C97" s="35">
+        <f t="shared" si="2"/>
         <v>3292.4166666666665</v>
       </c>
-      <c r="D20" s="8">
-        <v>221.58333333333348</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
+      <c r="D97" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E97" s="36"/>
+      <c r="F97" s="36"/>
+      <c r="G97" s="36"/>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A98" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B21">
+      <c r="B98" s="33">
+        <f t="shared" si="2"/>
         <v>3552</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C98" s="35">
+        <f t="shared" si="2"/>
         <v>3281.0833333333335</v>
       </c>
-      <c r="D21" s="8">
-        <v>270.91666666666652</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
+      <c r="D98" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E98" s="36"/>
+      <c r="F98" s="36"/>
+      <c r="G98" s="36"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A99" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B22">
+      <c r="B99" s="33">
+        <f t="shared" si="2"/>
         <v>3490</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C99" s="35">
+        <f t="shared" si="2"/>
         <v>3270.2083333333335</v>
       </c>
-      <c r="D22" s="8">
-        <v>219.79166666666652</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
+      <c r="D99" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E99" s="36"/>
+      <c r="F99" s="36"/>
+      <c r="G99" s="36"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B23">
+      <c r="B100" s="33">
+        <f t="shared" si="2"/>
         <v>3579</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C100" s="35">
+        <f t="shared" si="2"/>
         <v>3259.4583333333335</v>
       </c>
-      <c r="D23" s="8">
-        <v>319.54166666666652</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
+      <c r="D100" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E100" s="36"/>
+      <c r="F100" s="36"/>
+      <c r="G100" s="36"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A101" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B24">
+      <c r="B101" s="33">
+        <f t="shared" si="2"/>
         <v>3657</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C101" s="35">
+        <f t="shared" si="2"/>
         <v>3261.1666666666665</v>
       </c>
-      <c r="D24" s="8">
-        <v>395.83333333333348</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
+      <c r="D101" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E101" s="36"/>
+      <c r="F101" s="36"/>
+      <c r="G101" s="36"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A102" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B25">
+      <c r="B102" s="33">
+        <f t="shared" si="2"/>
         <v>3250</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C102" s="35">
+        <f t="shared" si="2"/>
         <v>3264.25</v>
       </c>
-      <c r="D25" s="8">
-        <v>-14.25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
+      <c r="D102" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E102" s="36"/>
+      <c r="F102" s="36"/>
+      <c r="G102" s="36"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A103" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B26">
+      <c r="B103" s="33">
+        <f t="shared" si="2"/>
         <v>3181</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C103" s="35">
+        <f t="shared" si="2"/>
         <v>3260.4583333333335</v>
       </c>
-      <c r="D26" s="8">
-        <v>-79.458333333333485</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
+      <c r="D103" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E103" s="36"/>
+      <c r="F103" s="36"/>
+      <c r="G103" s="36"/>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A104" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B27">
+      <c r="B104" s="33">
+        <f t="shared" si="2"/>
         <v>2948</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C104" s="35">
+        <f t="shared" si="2"/>
         <v>3256.7083333333335</v>
       </c>
-      <c r="D27" s="8">
-        <v>-308.70833333333348</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
+      <c r="D104" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E104" s="36"/>
+      <c r="F104" s="36"/>
+      <c r="G104" s="36"/>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A105" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B28">
+      <c r="B105" s="33">
+        <f t="shared" si="2"/>
         <v>2535</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C105" s="35">
+        <f t="shared" si="2"/>
         <v>3262.125</v>
       </c>
-      <c r="D28" s="8">
-        <v>-727.125</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
+      <c r="D105" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E105" s="36"/>
+      <c r="F105" s="36"/>
+      <c r="G105" s="36"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A106" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B29">
+      <c r="B106" s="33">
+        <f t="shared" si="2"/>
         <v>2956</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C106" s="35">
+        <f t="shared" si="2"/>
         <v>3267.0833333333335</v>
       </c>
-      <c r="D29" s="8">
-        <v>-311.08333333333348</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="4" t="s">
+      <c r="D106" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E106" s="36"/>
+      <c r="F106" s="36"/>
+      <c r="G106" s="36"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A107" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B30">
+      <c r="B107" s="33">
+        <f t="shared" si="2"/>
         <v>3079</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C107" s="35">
+        <f t="shared" si="2"/>
         <v>3259.2916666666665</v>
       </c>
-      <c r="D30" s="8">
-        <v>-180.29166666666652</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="4" t="s">
+      <c r="D107" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E107" s="36"/>
+      <c r="F107" s="36"/>
+      <c r="G107" s="36"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A108" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B31">
+      <c r="B108" s="33">
+        <f t="shared" si="2"/>
         <v>3417</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C108" s="35">
+        <f t="shared" si="2"/>
         <v>3254</v>
       </c>
-      <c r="D31" s="8">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="4" t="s">
+      <c r="D108" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E108" s="36"/>
+      <c r="F108" s="36"/>
+      <c r="G108" s="36"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A109" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B32">
+      <c r="B109" s="33">
+        <f t="shared" si="2"/>
         <v>3449</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C109" s="35">
+        <f t="shared" si="2"/>
         <v>3256.9583333333335</v>
       </c>
-      <c r="D32" s="8">
-        <v>192.04166666666652</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33">
-        <v>3527</v>
-      </c>
-      <c r="C33" s="1">
-        <v>3256.7083333333335</v>
-      </c>
-      <c r="D33" s="8">
-        <v>270.29166666666652</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34">
-        <v>3645</v>
-      </c>
-      <c r="C34" s="1">
-        <v>3269</v>
-      </c>
-      <c r="D34" s="8">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35">
-        <v>3543</v>
-      </c>
-      <c r="C35" s="1">
-        <v>3279.0833333333335</v>
-      </c>
-      <c r="D35" s="8">
-        <v>263.91666666666652</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36">
-        <v>3506</v>
-      </c>
-      <c r="C36" s="1">
-        <v>3252.8333333333335</v>
-      </c>
-      <c r="D36" s="8">
-        <v>253.16666666666652</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37">
-        <v>3274</v>
-      </c>
-      <c r="C37" s="1">
-        <v>3228.0416666666665</v>
-      </c>
-      <c r="D37" s="8">
-        <v>45.958333333333485</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38">
-        <v>3228</v>
-      </c>
-      <c r="C38" s="1">
-        <v>3248.2083333333335</v>
-      </c>
-      <c r="D38" s="8">
-        <v>-20.208333333333485</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39">
-        <v>2895</v>
-      </c>
-      <c r="C39" s="1">
-        <v>3294.2916666666665</v>
-      </c>
-      <c r="D39" s="8">
-        <v>-399.29166666666652</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40">
-        <v>2883</v>
-      </c>
-      <c r="C40" s="1">
-        <v>3340.3333333333335</v>
-      </c>
-      <c r="D40" s="8">
-        <v>-457.33333333333348</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41">
-        <v>2850</v>
-      </c>
-      <c r="C41" s="1">
-        <v>3384.6666666666665</v>
-      </c>
-      <c r="D41" s="8">
-        <v>-534.66666666666652</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42">
-        <v>2555</v>
-      </c>
-      <c r="C42" s="1">
-        <v>3433.5416666666665</v>
-      </c>
-      <c r="D42" s="8">
-        <v>-878.54166666666652</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43">
-        <v>3346</v>
-      </c>
-      <c r="C43" s="1">
-        <v>3481.2916666666665</v>
-      </c>
-      <c r="D43" s="8">
-        <v>-135.29166666666652</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44">
-        <v>4004</v>
-      </c>
-      <c r="C44" s="1">
-        <v>3514.8333333333335</v>
-      </c>
-      <c r="D44" s="8">
-        <v>489.16666666666652</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B45">
-        <v>4078</v>
-      </c>
-      <c r="C45" s="1">
-        <v>3549.875</v>
-      </c>
-      <c r="D45" s="8">
-        <v>528.125</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B46">
-        <v>4199</v>
-      </c>
-      <c r="C46" s="1">
-        <v>3567.7083333333335</v>
-      </c>
-      <c r="D46" s="8">
-        <v>631.29166666666652</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B47">
-        <v>4053</v>
-      </c>
-      <c r="C47" s="1">
-        <v>3590.6666666666665</v>
-      </c>
-      <c r="D47" s="8">
-        <v>462.33333333333348</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B48">
-        <v>4169</v>
-      </c>
-      <c r="C48" s="1">
-        <v>3672.125</v>
-      </c>
-      <c r="D48" s="8">
-        <v>496.875</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B49">
-        <v>3757</v>
-      </c>
-      <c r="C49" s="1">
-        <v>3758.1666666666665</v>
-      </c>
-      <c r="D49" s="8">
-        <v>-1.1666666666665151</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B50">
-        <v>3550</v>
-      </c>
-      <c r="C50" s="1">
-        <v>3793.7916666666665</v>
-      </c>
-      <c r="D50" s="8">
-        <v>-243.79166666666652</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B51">
-        <v>3414</v>
-      </c>
-      <c r="C51" s="1">
-        <v>3804.8333333333335</v>
-      </c>
-      <c r="D51" s="8">
-        <v>-390.83333333333348</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B52">
-        <v>2792</v>
-      </c>
-      <c r="C52" s="1">
-        <v>3816.625</v>
-      </c>
-      <c r="D52" s="8">
-        <v>-1024.625</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B53">
-        <v>3492</v>
-      </c>
-      <c r="C53" s="1">
-        <v>3830.9583333333335</v>
-      </c>
-      <c r="D53" s="8">
-        <v>-338.95833333333348</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B54">
-        <v>3868</v>
-      </c>
-      <c r="C54" s="1">
-        <v>3853.2916666666665</v>
-      </c>
-      <c r="D54" s="8">
-        <v>14.708333333333485</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B55">
-        <v>4098</v>
-      </c>
-      <c r="C55" s="1">
-        <v>3875.5</v>
-      </c>
-      <c r="D55" s="8">
-        <v>222.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B56">
-        <v>4107</v>
-      </c>
-      <c r="C56" s="1">
-        <v>3899.8333333333335</v>
-      </c>
-      <c r="D56" s="8">
-        <v>207.16666666666652</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B57">
-        <v>4240</v>
-      </c>
-      <c r="C57" t="s">
-        <v>79</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B58">
-        <v>4320</v>
-      </c>
-      <c r="C58" t="s">
-        <v>79</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B59">
-        <v>4276</v>
-      </c>
-      <c r="C59" t="s">
-        <v>79</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B60">
-        <v>4482</v>
-      </c>
-      <c r="C60" t="s">
-        <v>79</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B61">
-        <v>3977</v>
-      </c>
-      <c r="C61" t="s">
-        <v>79</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B62" s="13">
-        <v>3914</v>
-      </c>
-      <c r="C62" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D62" s="14" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" ht="34.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="B65" s="35"/>
-      <c r="C65" s="35"/>
-      <c r="D65" s="35"/>
-      <c r="E65" s="35"/>
-      <c r="F65" s="35"/>
-      <c r="G65" s="35"/>
-      <c r="H65" s="35"/>
-      <c r="I65" s="35"/>
-      <c r="J65" s="35"/>
-      <c r="K65" s="35"/>
-      <c r="L65" s="35"/>
-      <c r="M65" s="35"/>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A66" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="B66" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="C66" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="D66" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="E66" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="F66" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="G66" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="H66" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I66" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="J66" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="K66" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="L66" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="M66" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="N66" s="9"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A67" s="28">
-        <v>2017</v>
-      </c>
-      <c r="B67" t="s">
-        <v>79</v>
-      </c>
-      <c r="C67" t="s">
-        <v>79</v>
-      </c>
-      <c r="D67" t="s">
-        <v>79</v>
-      </c>
-      <c r="E67" t="s">
-        <v>79</v>
-      </c>
-      <c r="F67" t="s">
-        <v>79</v>
-      </c>
-      <c r="G67" t="s">
-        <v>79</v>
-      </c>
-      <c r="H67" s="39"/>
-      <c r="I67" s="39"/>
-      <c r="J67" s="39"/>
-      <c r="K67" s="39"/>
-      <c r="L67" s="39"/>
-      <c r="M67" s="39"/>
-      <c r="N67" s="10"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A68" s="28">
-        <v>2018</v>
-      </c>
-      <c r="B68" s="39"/>
-      <c r="C68" s="39"/>
-      <c r="D68" s="1">
-        <v>-296.70833333333348</v>
-      </c>
-      <c r="E68" s="1">
-        <v>-334.16666666666652</v>
-      </c>
-      <c r="F68" s="1">
-        <v>135.25</v>
-      </c>
-      <c r="G68" s="1">
-        <v>221.58333333333348</v>
-      </c>
-      <c r="H68" s="1">
-        <v>270.91666666666652</v>
-      </c>
-      <c r="I68" s="1">
-        <v>219.79166666666652</v>
-      </c>
-      <c r="J68" s="1">
-        <v>319.54166666666652</v>
-      </c>
-      <c r="K68" s="1">
-        <v>395.83333333333348</v>
-      </c>
-      <c r="L68" s="1">
-        <v>-14.25</v>
-      </c>
-      <c r="M68" s="8">
-        <v>-79.458333333333485</v>
-      </c>
-      <c r="N68" s="10"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A69" s="28">
-        <v>2019</v>
-      </c>
-      <c r="B69" s="1">
-        <v>-308.70833333333348</v>
-      </c>
-      <c r="C69" s="1">
-        <v>-727.125</v>
-      </c>
-      <c r="D69" s="1">
-        <v>-311.08333333333348</v>
-      </c>
-      <c r="E69" s="1">
-        <v>-180.29166666666652</v>
-      </c>
-      <c r="F69" s="1">
-        <v>163</v>
-      </c>
-      <c r="G69" s="1">
-        <v>192.04166666666652</v>
-      </c>
-      <c r="H69" s="1">
-        <v>270.29166666666652</v>
-      </c>
-      <c r="I69" s="1">
-        <v>376</v>
-      </c>
-      <c r="J69" s="1">
-        <v>263.91666666666652</v>
-      </c>
-      <c r="K69" s="1">
-        <v>253.16666666666652</v>
-      </c>
-      <c r="L69" s="1">
-        <v>45.958333333333485</v>
-      </c>
-      <c r="M69" s="8">
-        <v>-20.208333333333485</v>
-      </c>
-      <c r="N69" s="10"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A70" s="28">
-        <v>2020</v>
-      </c>
-      <c r="B70" s="1">
-        <v>-399.29166666666652</v>
-      </c>
-      <c r="C70" s="1">
-        <v>-457.33333333333348</v>
-      </c>
-      <c r="D70" s="1">
-        <v>-534.66666666666652</v>
-      </c>
-      <c r="E70" s="1">
-        <v>-878.54166666666652</v>
-      </c>
-      <c r="F70" s="1">
-        <v>-135.29166666666652</v>
-      </c>
-      <c r="G70" s="1">
-        <v>489.16666666666652</v>
-      </c>
-      <c r="H70" s="1">
-        <v>528.125</v>
-      </c>
-      <c r="I70" s="1">
-        <v>631.29166666666652</v>
-      </c>
-      <c r="J70" s="1">
-        <v>462.33333333333348</v>
-      </c>
-      <c r="K70" s="1">
-        <v>496.875</v>
-      </c>
-      <c r="L70" s="1">
-        <v>-1.1666666666665151</v>
-      </c>
-      <c r="M70" s="8">
-        <v>-243.79166666666652</v>
-      </c>
-      <c r="N70" s="29" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A71" s="28">
-        <v>2021</v>
-      </c>
-      <c r="B71" s="1">
-        <v>-390.83333333333348</v>
-      </c>
-      <c r="C71" s="1">
-        <v>-1024.625</v>
-      </c>
-      <c r="D71" s="1">
-        <v>-338.95833333333348</v>
-      </c>
-      <c r="E71" s="1">
-        <v>14.708333333333485</v>
-      </c>
-      <c r="F71" s="1">
-        <v>222.5</v>
-      </c>
-      <c r="G71" s="1">
-        <v>207.16666666666652</v>
-      </c>
-      <c r="H71" t="s">
-        <v>79</v>
-      </c>
-      <c r="I71" t="s">
-        <v>79</v>
-      </c>
-      <c r="J71" t="s">
-        <v>79</v>
-      </c>
-      <c r="K71" t="s">
-        <v>79</v>
-      </c>
-      <c r="L71" t="s">
-        <v>79</v>
-      </c>
-      <c r="M71" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="N71" s="30"/>
-    </row>
-    <row r="72" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="B72" s="1">
-        <v>-350.22916666666674</v>
-      </c>
-      <c r="C72" s="1">
-        <v>-695.78125</v>
-      </c>
-      <c r="D72" s="1">
-        <v>-370.35416666666674</v>
-      </c>
-      <c r="E72" s="1">
-        <v>-344.57291666666652</v>
-      </c>
-      <c r="F72" s="1">
-        <v>96.364583333333371</v>
-      </c>
-      <c r="G72" s="1">
-        <v>277.48958333333326</v>
-      </c>
-      <c r="H72" s="1">
-        <v>361.93749999999989</v>
-      </c>
-      <c r="I72" s="1">
-        <v>321.52083333333326</v>
-      </c>
-      <c r="J72" s="1">
-        <v>318.64583333333326</v>
-      </c>
-      <c r="K72" s="1">
-        <v>362.16666666666663</v>
-      </c>
-      <c r="L72" s="39"/>
-      <c r="M72" s="39"/>
-      <c r="N72" s="11">
-        <v>-5.0060763888889142</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" ht="19.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="25"/>
-      <c r="B73" s="7">
-        <v>-345.22309027777783</v>
-      </c>
-      <c r="C73" s="39"/>
-      <c r="D73" s="39"/>
-      <c r="E73" s="39"/>
-      <c r="F73" s="39"/>
-      <c r="G73" s="39"/>
-      <c r="H73" s="39"/>
-      <c r="I73" s="39"/>
-      <c r="J73" s="39"/>
-      <c r="K73" s="39"/>
-      <c r="L73" s="39"/>
-      <c r="M73" s="39"/>
-      <c r="N73" s="12"/>
-    </row>
-    <row r="76" spans="1:14" ht="43.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A76" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="B76" s="32"/>
-      <c r="C76" s="32"/>
-      <c r="D76" s="32"/>
-      <c r="E76" s="32"/>
-      <c r="F76" s="32"/>
-      <c r="G76" s="33"/>
-    </row>
-    <row r="77" spans="1:14" ht="37.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="18" t="s">
+      <c r="D109" s="37">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="B77" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="C77" s="20"/>
-      <c r="D77" s="20"/>
-      <c r="E77" s="20"/>
-      <c r="F77" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G77" s="21" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A78" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B78">
-        <v>3034</v>
-      </c>
-      <c r="C78" t="s">
-        <v>79</v>
-      </c>
-      <c r="D78" t="s">
-        <v>79</v>
-      </c>
-      <c r="E78" s="39"/>
-      <c r="F78" t="s">
-        <v>79</v>
-      </c>
-      <c r="G78" s="39"/>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A79" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B79">
-        <v>2748</v>
-      </c>
-      <c r="C79" t="s">
-        <v>79</v>
-      </c>
-      <c r="D79" t="s">
-        <v>79</v>
-      </c>
-      <c r="E79" s="39"/>
-      <c r="F79" t="s">
-        <v>79</v>
-      </c>
-      <c r="G79" s="39"/>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A80" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B80">
-        <v>3164</v>
-      </c>
-      <c r="C80" t="s">
-        <v>79</v>
-      </c>
-      <c r="D80" t="s">
-        <v>79</v>
-      </c>
-      <c r="E80" s="39"/>
-      <c r="F80" t="s">
-        <v>79</v>
-      </c>
-      <c r="G80" s="39"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A81" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B81">
-        <v>3238</v>
-      </c>
-      <c r="C81" t="s">
-        <v>79</v>
-      </c>
-      <c r="D81" t="s">
-        <v>79</v>
-      </c>
-      <c r="E81" s="39"/>
-      <c r="F81" t="s">
-        <v>79</v>
-      </c>
-      <c r="G81" s="39"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A82" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B82">
-        <v>3416</v>
-      </c>
-      <c r="C82" t="s">
-        <v>79</v>
-      </c>
-      <c r="D82" t="s">
-        <v>79</v>
-      </c>
-      <c r="E82" s="39"/>
-      <c r="F82" t="s">
-        <v>79</v>
-      </c>
-      <c r="G82" s="39"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A83" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B83">
-        <v>3492</v>
-      </c>
-      <c r="C83" t="s">
-        <v>79</v>
-      </c>
-      <c r="D83" t="s">
-        <v>79</v>
-      </c>
-      <c r="E83" s="39"/>
-      <c r="F83" t="s">
-        <v>79</v>
-      </c>
-      <c r="G83" s="39"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A84" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B84">
-        <v>3730</v>
-      </c>
-      <c r="C84" s="1">
-        <v>3351.5833333333335</v>
-      </c>
-      <c r="D84" s="1">
-        <v>378.41666666666652</v>
-      </c>
-      <c r="E84" s="39"/>
-      <c r="F84" s="39"/>
-      <c r="G84" s="39"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A85" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B85">
-        <v>3409</v>
-      </c>
-      <c r="C85" s="1">
-        <v>3350</v>
-      </c>
-      <c r="D85" s="1">
-        <v>59</v>
-      </c>
-      <c r="E85" s="39"/>
-      <c r="F85" s="39"/>
-      <c r="G85" s="39"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A86" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B86">
-        <v>3572</v>
-      </c>
-      <c r="C86" s="1">
-        <v>3343.2083333333335</v>
-      </c>
-      <c r="D86" s="1">
-        <v>228.79166666666652</v>
-      </c>
-      <c r="E86" s="39"/>
-      <c r="F86" s="39"/>
-      <c r="G86" s="39"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A87" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B87">
-        <v>3629</v>
-      </c>
-      <c r="C87" s="1">
-        <v>3326.2083333333335</v>
-      </c>
-      <c r="D87" s="1">
-        <v>302.79166666666652</v>
-      </c>
-      <c r="E87" s="39"/>
-      <c r="F87" s="39"/>
-      <c r="G87" s="39"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A88" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B88">
-        <v>3408</v>
-      </c>
-      <c r="C88" s="1">
-        <v>3316.5416666666665</v>
-      </c>
-      <c r="D88" s="1">
-        <v>91.458333333333485</v>
-      </c>
-      <c r="E88" s="39"/>
-      <c r="F88" s="39"/>
-      <c r="G88" s="39"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A89" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89">
-        <v>3391</v>
-      </c>
-      <c r="C89" s="1">
-        <v>3318.5833333333335</v>
-      </c>
-      <c r="D89" s="1">
-        <v>72.416666666666515</v>
-      </c>
-      <c r="E89" s="39"/>
-      <c r="F89" s="39"/>
-      <c r="G89" s="39"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A90" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B90">
-        <v>3010</v>
-      </c>
-      <c r="C90" s="1">
-        <v>3312.0833333333335</v>
-      </c>
-      <c r="D90" s="1">
-        <v>-302.08333333333348</v>
-      </c>
-      <c r="E90" s="39"/>
-      <c r="F90" s="39"/>
-      <c r="G90" s="39"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A91" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B91">
-        <v>2734</v>
-      </c>
-      <c r="C91" s="1">
-        <v>3308.0416666666665</v>
-      </c>
-      <c r="D91" s="1">
-        <v>-574.04166666666652</v>
-      </c>
-      <c r="E91" s="39"/>
-      <c r="F91" s="39"/>
-      <c r="G91" s="39"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A92" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B92">
-        <v>3015</v>
-      </c>
-      <c r="C92" s="1">
-        <v>3311.7083333333335</v>
-      </c>
-      <c r="D92" s="1">
-        <v>-296.70833333333348</v>
-      </c>
-      <c r="E92" s="39"/>
-      <c r="F92" s="39"/>
-      <c r="G92" s="39"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A93" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B93">
-        <v>2979</v>
-      </c>
-      <c r="C93" s="1">
-        <v>3313.1666666666665</v>
-      </c>
-      <c r="D93" s="1">
-        <v>-334.16666666666652</v>
-      </c>
-      <c r="E93" s="39"/>
-      <c r="F93" s="39"/>
-      <c r="G93" s="39"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A94" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B94">
-        <v>3443</v>
-      </c>
-      <c r="C94" s="1">
-        <v>3307.75</v>
-      </c>
-      <c r="D94" s="1">
-        <v>135.25</v>
-      </c>
-      <c r="E94" s="1">
-        <v>101.37065972222229</v>
-      </c>
-      <c r="F94" s="1">
-        <v>33.879340277777715</v>
-      </c>
-      <c r="G94" s="8">
-        <v>3341.6293402777778</v>
-      </c>
-      <c r="H94" s="1"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A95" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B95">
-        <v>3514</v>
-      </c>
-      <c r="C95" s="1">
-        <v>3292.4166666666665</v>
-      </c>
-      <c r="D95" s="1">
-        <v>221.58333333333348</v>
-      </c>
-      <c r="E95" s="1">
-        <v>282.49565972222217</v>
-      </c>
-      <c r="F95" s="1">
-        <v>-60.912326388888687</v>
-      </c>
-      <c r="G95" s="8">
-        <v>3231.5043402777778</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A96" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B96">
-        <v>3552</v>
-      </c>
-      <c r="C96" s="1">
-        <v>3281.0833333333335</v>
-      </c>
-      <c r="D96" s="1">
-        <v>270.91666666666652</v>
-      </c>
-      <c r="E96" s="1">
-        <v>366.9435763888888</v>
-      </c>
-      <c r="F96" s="1">
-        <v>-96.026909722222285</v>
-      </c>
-      <c r="G96" s="8">
-        <v>3185.0564236111113</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A97" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B97">
-        <v>3490</v>
-      </c>
-      <c r="C97" s="1">
-        <v>3270.2083333333335</v>
-      </c>
-      <c r="D97" s="1">
-        <v>219.79166666666652</v>
-      </c>
-      <c r="E97" s="1">
-        <v>326.52690972222217</v>
-      </c>
-      <c r="F97" s="1">
-        <v>-106.73524305555566</v>
-      </c>
-      <c r="G97" s="8">
-        <v>3163.4730902777778</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A98" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B98">
-        <v>3579</v>
-      </c>
-      <c r="C98" s="1">
-        <v>3259.4583333333335</v>
-      </c>
-      <c r="D98" s="1">
-        <v>319.54166666666652</v>
-      </c>
-      <c r="E98" s="1">
-        <v>323.65190972222217</v>
-      </c>
-      <c r="F98" s="1">
-        <v>-4.1102430555556566</v>
-      </c>
-      <c r="G98" s="8">
-        <v>3255.3480902777778</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A99" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B99">
-        <v>3657</v>
-      </c>
-      <c r="C99" s="1">
-        <v>3261.1666666666665</v>
-      </c>
-      <c r="D99" s="1">
-        <v>395.83333333333348</v>
-      </c>
-      <c r="E99" s="1">
-        <v>367.17274305555554</v>
-      </c>
-      <c r="F99" s="1">
-        <v>28.660590277777942</v>
-      </c>
-      <c r="G99" s="8">
-        <v>3289.8272569444443</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A100" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B100">
-        <v>3250</v>
-      </c>
-      <c r="C100" s="1">
-        <v>3264.25</v>
-      </c>
-      <c r="D100" s="1">
-        <v>-14.25</v>
-      </c>
-      <c r="E100" s="1">
-        <v>35.506076388889028</v>
-      </c>
-      <c r="F100" s="1">
-        <v>-49.756076388889028</v>
-      </c>
-      <c r="G100" s="8">
-        <v>3214.4939236111109</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A101" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B101">
-        <v>3181</v>
-      </c>
-      <c r="C101" s="1">
-        <v>3260.4583333333335</v>
-      </c>
-      <c r="D101" s="1">
-        <v>-79.458333333333485</v>
-      </c>
-      <c r="E101" s="1">
-        <v>-62.754340277777828</v>
-      </c>
-      <c r="F101" s="1">
-        <v>-16.703993055555657</v>
-      </c>
-      <c r="G101" s="8">
-        <v>3243.7543402777778</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A102" s="6"/>
-      <c r="B102" s="13"/>
-      <c r="C102" s="13"/>
-      <c r="D102" s="13"/>
-      <c r="E102" s="13"/>
-      <c r="F102" s="13"/>
-      <c r="G102" s="14"/>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H107" s="1"/>
-      <c r="I107" s="1"/>
-      <c r="J107" s="1"/>
-      <c r="K107" s="1"/>
-      <c r="L107" s="1"/>
-      <c r="M107" s="1"/>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-      <c r="D108" s="1"/>
-      <c r="E108" s="1"/>
-      <c r="F108" s="1"/>
-      <c r="G108" s="1"/>
-      <c r="H108" s="1"/>
-      <c r="I108" s="1"/>
-      <c r="J108" s="1"/>
-      <c r="K108" s="1"/>
-      <c r="L108" s="1"/>
-      <c r="M108" s="1"/>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
-      <c r="D109" s="1"/>
-      <c r="E109" s="1"/>
-      <c r="F109" s="1"/>
-      <c r="G109" s="1"/>
+      <c r="E109" s="36"/>
+      <c r="F109" s="36"/>
+      <c r="G109" s="36"/>
       <c r="H109" s="1"/>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
@@ -6011,12 +5350,24 @@
       <c r="M109" s="1"/>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
-      <c r="E110" s="1"/>
-      <c r="F110" s="1"/>
-      <c r="G110" s="1"/>
+      <c r="A110" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B110" s="33">
+        <f t="shared" si="2"/>
+        <v>3527</v>
+      </c>
+      <c r="C110" s="35">
+        <f t="shared" si="2"/>
+        <v>3256.7083333333335</v>
+      </c>
+      <c r="D110" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E110" s="36"/>
+      <c r="F110" s="36"/>
+      <c r="G110" s="36"/>
       <c r="H110" s="1"/>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
@@ -6024,22 +5375,51 @@
       <c r="L110" s="1"/>
       <c r="M110" s="1"/>
     </row>
-    <row r="111" spans="1:13" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
-      <c r="D111" s="1"/>
-      <c r="E111" s="1"/>
-      <c r="F111" s="1"/>
-      <c r="G111" s="1"/>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A111" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B111" s="33">
+        <f t="shared" si="2"/>
+        <v>3645</v>
+      </c>
+      <c r="C111" s="35">
+        <f t="shared" si="2"/>
+        <v>3269</v>
+      </c>
+      <c r="D111" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E111" s="36"/>
+      <c r="F111" s="36"/>
+      <c r="G111" s="36"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1"/>
+      <c r="K111" s="1"/>
+      <c r="L111" s="1"/>
+      <c r="M111" s="1"/>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A112" s="2"/>
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
-      <c r="E112" s="1"/>
-      <c r="F112" s="1"/>
-      <c r="G112" s="1"/>
+      <c r="A112" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B112" s="33">
+        <f t="shared" si="2"/>
+        <v>3543</v>
+      </c>
+      <c r="C112" s="35">
+        <f t="shared" si="2"/>
+        <v>3279.0833333333335</v>
+      </c>
+      <c r="D112" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E112" s="36"/>
+      <c r="F112" s="36"/>
+      <c r="G112" s="36"/>
       <c r="H112" s="1"/>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
@@ -6047,27 +5427,565 @@
       <c r="L112" s="1"/>
       <c r="M112" s="1"/>
     </row>
-    <row r="113" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B113" s="1"/>
-      <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
-      <c r="E113" s="1"/>
-      <c r="F113" s="1"/>
-      <c r="G113" s="1"/>
-      <c r="H113" s="1"/>
-      <c r="I113" s="1"/>
-      <c r="J113" s="1"/>
-      <c r="K113" s="1"/>
-      <c r="L113" s="1"/>
-      <c r="M113" s="1"/>
-      <c r="N113" s="1"/>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A113" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B113" s="33">
+        <f t="shared" ref="B113:D128" si="3">B36</f>
+        <v>3506</v>
+      </c>
+      <c r="C113" s="35">
+        <f t="shared" si="3"/>
+        <v>3252.8333333333335</v>
+      </c>
+      <c r="D113" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E113" s="36"/>
+      <c r="F113" s="36"/>
+      <c r="G113" s="36"/>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A114" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B114" s="33">
+        <f t="shared" si="3"/>
+        <v>3274</v>
+      </c>
+      <c r="C114" s="35">
+        <f t="shared" si="3"/>
+        <v>3228.0416666666665</v>
+      </c>
+      <c r="D114" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E114" s="36"/>
+      <c r="F114" s="36"/>
+      <c r="G114" s="36"/>
+      <c r="H114" s="1"/>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1"/>
+      <c r="K114" s="1"/>
+      <c r="L114" s="1"/>
+      <c r="M114" s="1"/>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A115" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B115" s="33">
+        <f t="shared" si="3"/>
+        <v>3228</v>
+      </c>
+      <c r="C115" s="35">
+        <f t="shared" si="3"/>
+        <v>3248.2083333333335</v>
+      </c>
+      <c r="D115" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E115" s="36"/>
+      <c r="F115" s="36"/>
+      <c r="G115" s="36"/>
+      <c r="H115" s="1"/>
+      <c r="I115" s="1"/>
+      <c r="J115" s="1"/>
+      <c r="K115" s="1"/>
+      <c r="L115" s="1"/>
+      <c r="M115" s="1"/>
+      <c r="N115" s="1"/>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A116" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B116" s="33">
+        <f t="shared" si="3"/>
+        <v>2895</v>
+      </c>
+      <c r="C116" s="35">
+        <f t="shared" si="3"/>
+        <v>3294.2916666666665</v>
+      </c>
+      <c r="D116" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E116" s="36"/>
+      <c r="F116" s="36"/>
+      <c r="G116" s="36"/>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A117" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B117" s="33">
+        <f t="shared" si="3"/>
+        <v>2883</v>
+      </c>
+      <c r="C117" s="35">
+        <f t="shared" si="3"/>
+        <v>3340.3333333333335</v>
+      </c>
+      <c r="D117" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E117" s="36"/>
+      <c r="F117" s="36"/>
+      <c r="G117" s="36"/>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A118" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B118" s="33">
+        <f t="shared" si="3"/>
+        <v>2850</v>
+      </c>
+      <c r="C118" s="35">
+        <f t="shared" si="3"/>
+        <v>3384.6666666666665</v>
+      </c>
+      <c r="D118" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E118" s="36"/>
+      <c r="F118" s="36"/>
+      <c r="G118" s="36"/>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A119" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B119" s="33">
+        <f t="shared" si="3"/>
+        <v>2555</v>
+      </c>
+      <c r="C119" s="35">
+        <f t="shared" si="3"/>
+        <v>3433.5416666666665</v>
+      </c>
+      <c r="D119" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E119" s="36"/>
+      <c r="F119" s="36"/>
+      <c r="G119" s="36"/>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A120" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B120" s="33">
+        <f t="shared" si="3"/>
+        <v>3346</v>
+      </c>
+      <c r="C120" s="35">
+        <f t="shared" si="3"/>
+        <v>3481.2916666666665</v>
+      </c>
+      <c r="D120" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E120" s="36"/>
+      <c r="F120" s="36"/>
+      <c r="G120" s="36"/>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A121" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B121" s="33">
+        <f t="shared" si="3"/>
+        <v>4004</v>
+      </c>
+      <c r="C121" s="35">
+        <f t="shared" si="3"/>
+        <v>3514.8333333333335</v>
+      </c>
+      <c r="D121" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+      <c r="G121" s="36"/>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A122" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B122" s="33">
+        <f t="shared" si="3"/>
+        <v>4078</v>
+      </c>
+      <c r="C122" s="35">
+        <f t="shared" si="3"/>
+        <v>3549.875</v>
+      </c>
+      <c r="D122" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E122" s="36"/>
+      <c r="F122" s="36"/>
+      <c r="G122" s="36"/>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A123" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B123" s="33">
+        <f t="shared" si="3"/>
+        <v>4199</v>
+      </c>
+      <c r="C123" s="35">
+        <f t="shared" si="3"/>
+        <v>3567.7083333333335</v>
+      </c>
+      <c r="D123" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E123" s="36"/>
+      <c r="F123" s="36"/>
+      <c r="G123" s="36"/>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A124" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B124" s="33">
+        <f t="shared" si="3"/>
+        <v>4053</v>
+      </c>
+      <c r="C124" s="35">
+        <f t="shared" si="3"/>
+        <v>3590.6666666666665</v>
+      </c>
+      <c r="D124" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E124" s="36"/>
+      <c r="F124" s="36"/>
+      <c r="G124" s="36"/>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A125" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B125" s="33">
+        <f t="shared" si="3"/>
+        <v>4169</v>
+      </c>
+      <c r="C125" s="35">
+        <f t="shared" si="3"/>
+        <v>3672.125</v>
+      </c>
+      <c r="D125" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E125" s="36"/>
+      <c r="F125" s="36"/>
+      <c r="G125" s="36"/>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A126" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B126" s="33">
+        <f t="shared" si="3"/>
+        <v>3757</v>
+      </c>
+      <c r="C126" s="35">
+        <f t="shared" si="3"/>
+        <v>3758.1666666666665</v>
+      </c>
+      <c r="D126" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E126" s="36"/>
+      <c r="F126" s="36"/>
+      <c r="G126" s="36"/>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A127" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B127" s="33">
+        <f t="shared" si="3"/>
+        <v>3550</v>
+      </c>
+      <c r="C127" s="35">
+        <f t="shared" si="3"/>
+        <v>3793.7916666666665</v>
+      </c>
+      <c r="D127" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E127" s="36"/>
+      <c r="F127" s="36"/>
+      <c r="G127" s="36"/>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A128" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B128" s="33">
+        <f t="shared" si="3"/>
+        <v>3414</v>
+      </c>
+      <c r="C128" s="35">
+        <f t="shared" si="3"/>
+        <v>3804.8333333333335</v>
+      </c>
+      <c r="D128" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E128" s="36"/>
+      <c r="F128" s="36"/>
+      <c r="G128" s="36"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A129" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B129" s="33">
+        <f t="shared" ref="B129:D139" si="4">B52</f>
+        <v>2792</v>
+      </c>
+      <c r="C129" s="35">
+        <f t="shared" si="4"/>
+        <v>3816.625</v>
+      </c>
+      <c r="D129" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E129" s="36"/>
+      <c r="F129" s="36"/>
+      <c r="G129" s="36"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A130" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B130" s="33">
+        <f t="shared" si="4"/>
+        <v>3492</v>
+      </c>
+      <c r="C130" s="35">
+        <f t="shared" si="4"/>
+        <v>3830.9583333333335</v>
+      </c>
+      <c r="D130" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E130" s="36"/>
+      <c r="F130" s="36"/>
+      <c r="G130" s="36"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A131" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B131" s="33">
+        <f t="shared" si="4"/>
+        <v>3868</v>
+      </c>
+      <c r="C131" s="35">
+        <f t="shared" si="4"/>
+        <v>3853.2916666666665</v>
+      </c>
+      <c r="D131" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E131" s="36"/>
+      <c r="F131" s="36"/>
+      <c r="G131" s="36"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A132" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B132" s="33">
+        <f t="shared" si="4"/>
+        <v>4098</v>
+      </c>
+      <c r="C132" s="35">
+        <f t="shared" si="4"/>
+        <v>3875.5</v>
+      </c>
+      <c r="D132" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E132" s="36"/>
+      <c r="F132" s="36"/>
+      <c r="G132" s="36"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A133" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B133" s="33">
+        <f t="shared" si="4"/>
+        <v>4107</v>
+      </c>
+      <c r="C133" s="35">
+        <f t="shared" si="4"/>
+        <v>3899.8333333333335</v>
+      </c>
+      <c r="D133" s="37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E133" s="36"/>
+      <c r="F133" s="36"/>
+      <c r="G133" s="36"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A134" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B134" s="33">
+        <f t="shared" si="4"/>
+        <v>4240</v>
+      </c>
+      <c r="C134" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>NA</v>
+      </c>
+      <c r="D134" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E134" s="36"/>
+      <c r="F134" s="36"/>
+      <c r="G134" s="36"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A135" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B135" s="33">
+        <f t="shared" si="4"/>
+        <v>4320</v>
+      </c>
+      <c r="C135" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>NA</v>
+      </c>
+      <c r="D135" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E135" s="36"/>
+      <c r="F135" s="36"/>
+      <c r="G135" s="36"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A136" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B136" s="33">
+        <f t="shared" si="4"/>
+        <v>4276</v>
+      </c>
+      <c r="C136" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>NA</v>
+      </c>
+      <c r="D136" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E136" s="36"/>
+      <c r="F136" s="36"/>
+      <c r="G136" s="36"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A137" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B137" s="33">
+        <f t="shared" si="4"/>
+        <v>4482</v>
+      </c>
+      <c r="C137" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>NA</v>
+      </c>
+      <c r="D137" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E137" s="36"/>
+      <c r="F137" s="36"/>
+      <c r="G137" s="36"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A138" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B138" s="33">
+        <f t="shared" si="4"/>
+        <v>3977</v>
+      </c>
+      <c r="C138" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>NA</v>
+      </c>
+      <c r="D138" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E138" s="36"/>
+      <c r="F138" s="36"/>
+      <c r="G138" s="36"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A139" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B139" s="38">
+        <f t="shared" si="4"/>
+        <v>3914</v>
+      </c>
+      <c r="C139" s="38" t="str">
+        <f t="shared" si="4"/>
+        <v>NA</v>
+      </c>
+      <c r="D139" s="39">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E139" s="36"/>
+      <c r="F139" s="36"/>
+      <c r="G139" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="N70:N71"/>
-    <mergeCell ref="A76:G76"/>
-    <mergeCell ref="A65:M65"/>
+    <mergeCell ref="A78:G78"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A66:M66"/>
+    <mergeCell ref="N71:N72"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6086,14 +6004,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010070F75838E79B0E48B83E8E3F5479A3A2" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2b0c304636f8f537543cd13f583db9d4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xmlns:ns4="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0f089f22c5ce4e61126931f7622145b2" ns3:_="" ns4:_="">
     <xsd:import namespace="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
@@ -6288,6 +6198,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
   <ds:schemaRefs>
@@ -6297,23 +6215,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E1B631-90B0-4D19-A35E-F8DC8BE167A4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a"/>
-    <ds:schemaRef ds:uri="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBDDC771-C014-4A48-9FCA-802C556EA1D0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6330,4 +6231,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E1B631-90B0-4D19-A35E-F8DC8BE167A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a"/>
+    <ds:schemaRef ds:uri="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/handouts/chapter_1_4_handout.xlsx
+++ b/handouts/chapter_1_4_handout.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\craigaj\Documents\GitHub\timeseries\handouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC944B35-E5FD-4906-9307-671D58DB5C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB479EB8-EC4C-47F2-BBD2-04049E53E882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-11055" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
   </bookViews>
@@ -94,9 +94,6 @@
 </t>
   </si>
   <si>
-    <t>Random</t>
-  </si>
-  <si>
     <t xml:space="preserve">Seasonally Adjusted
 </t>
   </si>
@@ -334,10 +331,15 @@
 Centered Moving Average,      , and the Estimated Monthly Additive Effect,</t>
   </si>
   <si>
-    <t>Table 3: Computation of        the Random Component and the Seasonally Adjusted Time Series</t>
-  </si>
-  <si>
     <t>Mean,</t>
+  </si>
+  <si>
+    <t>Table 3: Computation of        the Random Component 
+and the Seasonally Adjusted Time Series</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Random
+</t>
   </si>
 </sst>
 </file>
@@ -410,7 +412,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -481,17 +483,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -591,16 +582,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -610,38 +601,53 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -652,11 +658,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -664,32 +667,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1953,8 +1941,8 @@
       <xdr:rowOff>163195</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="320040" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="TextBox 14">
@@ -2003,7 +1991,7 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -2045,7 +2033,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="TextBox 14">
@@ -2170,7 +2158,7 @@
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1400" i="1">
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -2285,8 +2273,8 @@
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="379575" cy="250903"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="TextBox 16">
@@ -2328,7 +2316,6 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
-              <a:pPr/>
               <a14:m>
                 <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:acc>
@@ -2344,7 +2331,7 @@
                       <m:sSub>
                         <m:sSubPr>
                           <m:ctrlPr>
-                            <a:rPr lang="en-US" sz="1400" i="1">
+                            <a:rPr lang="en-US" sz="1400" b="0" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
                           </m:ctrlPr>
@@ -2390,7 +2377,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="TextBox 16">
@@ -2458,8 +2445,8 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>202565</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>399415</xdr:colOff>
       <xdr:row>77</xdr:row>
       <xdr:rowOff>77470</xdr:rowOff>
     </xdr:from>
@@ -2479,7 +2466,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1878965" y="15546070"/>
+              <a:off x="2923540" y="15003145"/>
               <a:ext cx="320040" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2558,7 +2545,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1878965" y="15546070"/>
+              <a:off x="2923540" y="15003145"/>
               <a:ext cx="320040" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2659,7 +2646,7 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -3169,8 +3156,8 @@
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="320040" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -3219,7 +3206,7 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -3261,7 +3248,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -3309,6 +3296,151 @@
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝑠 ̅_𝑡</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" sz="1400"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>256540</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>210586</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="320040" cy="221214"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="9" name="TextBox 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AEC3097-FCC7-2824-0FCB-A513C9E1F93E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4342765" y="15688711"/>
+              <a:ext cx="320040" cy="221214"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑧</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" sz="1400"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="9" name="TextBox 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AEC3097-FCC7-2824-0FCB-A513C9E1F93E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4342765" y="15688711"/>
+              <a:ext cx="320040" cy="221214"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1400" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑧_𝑡</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1400"/>
             </a:p>
@@ -3649,12 +3781,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="45.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="32"/>
+      <c r="A1" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="35"/>
     </row>
     <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
@@ -3668,796 +3800,796 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="33">
+        <v>3</v>
+      </c>
+      <c r="B3" s="23">
         <v>3034</v>
       </c>
-      <c r="C3" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>78</v>
+      <c r="C3" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="33">
+        <v>4</v>
+      </c>
+      <c r="B4" s="23">
         <v>2748</v>
       </c>
-      <c r="C4" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>78</v>
+      <c r="C4" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="33">
+        <v>5</v>
+      </c>
+      <c r="B5" s="23">
         <v>3164</v>
       </c>
-      <c r="C5" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>78</v>
+      <c r="C5" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="33">
+        <v>6</v>
+      </c>
+      <c r="B6" s="23">
         <v>3238</v>
       </c>
-      <c r="C6" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>78</v>
+      <c r="C6" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="33">
+        <v>7</v>
+      </c>
+      <c r="B7" s="23">
         <v>3416</v>
       </c>
-      <c r="C7" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>78</v>
+      <c r="C7" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="33">
+        <v>8</v>
+      </c>
+      <c r="B8" s="23">
         <v>3492</v>
       </c>
-      <c r="C8" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" s="34" t="s">
-        <v>78</v>
+      <c r="C8" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="33">
+        <v>9</v>
+      </c>
+      <c r="B9" s="23">
         <v>3730</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="25">
         <v>3351.5833333333335</v>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="27">
         <f>IFERROR(B9-C9, "NA")</f>
         <v>378.41666666666652</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="33">
+        <v>10</v>
+      </c>
+      <c r="B10" s="23">
         <v>3409</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="25">
         <v>3350</v>
       </c>
-      <c r="D10" s="36"/>
+      <c r="D10" s="26"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="33">
+        <v>11</v>
+      </c>
+      <c r="B11" s="23">
         <v>3572</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="25">
         <v>3343.2083333333335</v>
       </c>
-      <c r="D11" s="36"/>
+      <c r="D11" s="26"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="33">
+        <v>12</v>
+      </c>
+      <c r="B12" s="23">
         <v>3629</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="25">
         <v>3326.2083333333335</v>
       </c>
-      <c r="D12" s="36"/>
+      <c r="D12" s="26"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="33">
+        <v>13</v>
+      </c>
+      <c r="B13" s="23">
         <v>3408</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="25">
         <v>3316.5416666666665</v>
       </c>
-      <c r="D13" s="36"/>
+      <c r="D13" s="26"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="33">
+        <v>14</v>
+      </c>
+      <c r="B14" s="23">
         <v>3391</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="25">
         <v>3318.5833333333335</v>
       </c>
-      <c r="D14" s="36"/>
+      <c r="D14" s="26"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="33">
+        <v>15</v>
+      </c>
+      <c r="B15" s="23">
         <v>3010</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="25">
         <v>3312.0833333333335</v>
       </c>
-      <c r="D15" s="36"/>
+      <c r="D15" s="26"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="33">
+        <v>16</v>
+      </c>
+      <c r="B16" s="23">
         <v>2734</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="25">
         <v>3308.0416666666665</v>
       </c>
-      <c r="D16" s="36"/>
+      <c r="D16" s="26"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="33">
+        <v>17</v>
+      </c>
+      <c r="B17" s="23">
         <v>3015</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="25">
         <v>3311.7083333333335</v>
       </c>
-      <c r="D17" s="36"/>
+      <c r="D17" s="26"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="33">
+        <v>18</v>
+      </c>
+      <c r="B18" s="23">
         <v>2979</v>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="25">
         <v>3313.1666666666665</v>
       </c>
-      <c r="D18" s="36"/>
+      <c r="D18" s="26"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="33">
+        <v>19</v>
+      </c>
+      <c r="B19" s="23">
         <v>3443</v>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="25">
         <v>3307.75</v>
       </c>
-      <c r="D19" s="36"/>
+      <c r="D19" s="26"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="33">
+        <v>20</v>
+      </c>
+      <c r="B20" s="23">
         <v>3514</v>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="25">
         <v>3292.4166666666665</v>
       </c>
-      <c r="D20" s="36"/>
+      <c r="D20" s="26"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="33">
+        <v>21</v>
+      </c>
+      <c r="B21" s="23">
         <v>3552</v>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="25">
         <v>3281.0833333333335</v>
       </c>
-      <c r="D21" s="36"/>
+      <c r="D21" s="26"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="33">
+        <v>22</v>
+      </c>
+      <c r="B22" s="23">
         <v>3490</v>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="25">
         <v>3270.2083333333335</v>
       </c>
-      <c r="D22" s="36"/>
+      <c r="D22" s="26"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="33">
+        <v>23</v>
+      </c>
+      <c r="B23" s="23">
         <v>3579</v>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="25">
         <v>3259.4583333333335</v>
       </c>
-      <c r="D23" s="36"/>
+      <c r="D23" s="26"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="33">
+        <v>24</v>
+      </c>
+      <c r="B24" s="23">
         <v>3657</v>
       </c>
-      <c r="C24" s="35">
+      <c r="C24" s="25">
         <v>3261.1666666666665</v>
       </c>
-      <c r="D24" s="36"/>
+      <c r="D24" s="26"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="33">
+        <v>25</v>
+      </c>
+      <c r="B25" s="23">
         <v>3250</v>
       </c>
-      <c r="C25" s="35">
+      <c r="C25" s="25">
         <v>3264.25</v>
       </c>
-      <c r="D25" s="36"/>
+      <c r="D25" s="26"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="33">
+        <v>26</v>
+      </c>
+      <c r="B26" s="23">
         <v>3181</v>
       </c>
-      <c r="C26" s="35">
+      <c r="C26" s="25">
         <v>3260.4583333333335</v>
       </c>
-      <c r="D26" s="36"/>
+      <c r="D26" s="26"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="33">
+        <v>27</v>
+      </c>
+      <c r="B27" s="23">
         <v>2948</v>
       </c>
-      <c r="C27" s="35">
+      <c r="C27" s="25">
         <v>3256.7083333333335</v>
       </c>
-      <c r="D27" s="36"/>
+      <c r="D27" s="26"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="33">
+        <v>28</v>
+      </c>
+      <c r="B28" s="23">
         <v>2535</v>
       </c>
-      <c r="C28" s="35">
+      <c r="C28" s="25">
         <v>3262.125</v>
       </c>
-      <c r="D28" s="36"/>
+      <c r="D28" s="26"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="33">
+        <v>29</v>
+      </c>
+      <c r="B29" s="23">
         <v>2956</v>
       </c>
-      <c r="C29" s="35">
+      <c r="C29" s="25">
         <v>3267.0833333333335</v>
       </c>
-      <c r="D29" s="36"/>
+      <c r="D29" s="26"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" s="33">
+        <v>30</v>
+      </c>
+      <c r="B30" s="23">
         <v>3079</v>
       </c>
-      <c r="C30" s="35">
+      <c r="C30" s="25">
         <v>3259.2916666666665</v>
       </c>
-      <c r="D30" s="36"/>
+      <c r="D30" s="26"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" s="33">
+        <v>31</v>
+      </c>
+      <c r="B31" s="23">
         <v>3417</v>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="25">
         <v>3254</v>
       </c>
-      <c r="D31" s="36"/>
+      <c r="D31" s="26"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="33">
+        <v>32</v>
+      </c>
+      <c r="B32" s="23">
         <v>3449</v>
       </c>
-      <c r="C32" s="35">
+      <c r="C32" s="25">
         <v>3256.9583333333335</v>
       </c>
-      <c r="D32" s="36"/>
+      <c r="D32" s="26"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="33">
+        <v>33</v>
+      </c>
+      <c r="B33" s="23">
         <v>3527</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="25">
         <v>3256.7083333333335</v>
       </c>
-      <c r="D33" s="36"/>
+      <c r="D33" s="26"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="33">
+        <v>34</v>
+      </c>
+      <c r="B34" s="23">
         <v>3645</v>
       </c>
-      <c r="C34" s="35">
+      <c r="C34" s="25">
         <v>3269</v>
       </c>
-      <c r="D34" s="36"/>
+      <c r="D34" s="26"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="33">
+        <v>35</v>
+      </c>
+      <c r="B35" s="23">
         <v>3543</v>
       </c>
-      <c r="C35" s="35">
+      <c r="C35" s="25">
         <v>3279.0833333333335</v>
       </c>
-      <c r="D35" s="36"/>
+      <c r="D35" s="26"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="33">
+        <v>36</v>
+      </c>
+      <c r="B36" s="23">
         <v>3506</v>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="25">
         <v>3252.8333333333335</v>
       </c>
-      <c r="D36" s="36"/>
+      <c r="D36" s="26"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="33">
+        <v>37</v>
+      </c>
+      <c r="B37" s="23">
         <v>3274</v>
       </c>
-      <c r="C37" s="35">
+      <c r="C37" s="25">
         <v>3228.0416666666665</v>
       </c>
-      <c r="D37" s="36"/>
+      <c r="D37" s="26"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="33">
+        <v>38</v>
+      </c>
+      <c r="B38" s="23">
         <v>3228</v>
       </c>
-      <c r="C38" s="35">
+      <c r="C38" s="25">
         <v>3248.2083333333335</v>
       </c>
-      <c r="D38" s="36"/>
+      <c r="D38" s="26"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="33">
+        <v>39</v>
+      </c>
+      <c r="B39" s="23">
         <v>2895</v>
       </c>
-      <c r="C39" s="35">
+      <c r="C39" s="25">
         <v>3294.2916666666665</v>
       </c>
-      <c r="D39" s="36"/>
+      <c r="D39" s="26"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="33">
+        <v>40</v>
+      </c>
+      <c r="B40" s="23">
         <v>2883</v>
       </c>
-      <c r="C40" s="35">
+      <c r="C40" s="25">
         <v>3340.3333333333335</v>
       </c>
-      <c r="D40" s="36"/>
+      <c r="D40" s="26"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="33">
+        <v>41</v>
+      </c>
+      <c r="B41" s="23">
         <v>2850</v>
       </c>
-      <c r="C41" s="35">
+      <c r="C41" s="25">
         <v>3384.6666666666665</v>
       </c>
-      <c r="D41" s="36"/>
+      <c r="D41" s="26"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="33">
+        <v>42</v>
+      </c>
+      <c r="B42" s="23">
         <v>2555</v>
       </c>
-      <c r="C42" s="35">
+      <c r="C42" s="25">
         <v>3433.5416666666665</v>
       </c>
-      <c r="D42" s="36"/>
+      <c r="D42" s="26"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43" s="33">
+        <v>43</v>
+      </c>
+      <c r="B43" s="23">
         <v>3346</v>
       </c>
-      <c r="C43" s="35">
+      <c r="C43" s="25">
         <v>3481.2916666666665</v>
       </c>
-      <c r="D43" s="36"/>
+      <c r="D43" s="26"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" s="33">
+        <v>44</v>
+      </c>
+      <c r="B44" s="23">
         <v>4004</v>
       </c>
-      <c r="C44" s="35">
+      <c r="C44" s="25">
         <v>3514.8333333333335</v>
       </c>
-      <c r="D44" s="36"/>
+      <c r="D44" s="26"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B45" s="33">
+        <v>45</v>
+      </c>
+      <c r="B45" s="23">
         <v>4078</v>
       </c>
-      <c r="C45" s="35">
+      <c r="C45" s="25">
         <v>3549.875</v>
       </c>
-      <c r="D45" s="36"/>
+      <c r="D45" s="26"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B46" s="33">
+        <v>46</v>
+      </c>
+      <c r="B46" s="23">
         <v>4199</v>
       </c>
-      <c r="C46" s="35">
+      <c r="C46" s="25">
         <v>3567.7083333333335</v>
       </c>
-      <c r="D46" s="36"/>
+      <c r="D46" s="26"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B47" s="33">
+        <v>47</v>
+      </c>
+      <c r="B47" s="23">
         <v>4053</v>
       </c>
-      <c r="C47" s="35">
+      <c r="C47" s="25">
         <v>3590.6666666666665</v>
       </c>
-      <c r="D47" s="36"/>
+      <c r="D47" s="26"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B48" s="33">
+        <v>48</v>
+      </c>
+      <c r="B48" s="23">
         <v>4169</v>
       </c>
-      <c r="C48" s="35">
+      <c r="C48" s="25">
         <v>3672.125</v>
       </c>
-      <c r="D48" s="36"/>
+      <c r="D48" s="26"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B49" s="33">
+        <v>49</v>
+      </c>
+      <c r="B49" s="23">
         <v>3757</v>
       </c>
-      <c r="C49" s="35">
+      <c r="C49" s="25">
         <v>3758.1666666666665</v>
       </c>
-      <c r="D49" s="36"/>
+      <c r="D49" s="26"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B50" s="33">
+        <v>50</v>
+      </c>
+      <c r="B50" s="23">
         <v>3550</v>
       </c>
-      <c r="C50" s="35">
+      <c r="C50" s="25">
         <v>3793.7916666666665</v>
       </c>
-      <c r="D50" s="36"/>
+      <c r="D50" s="26"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B51" s="33">
+        <v>51</v>
+      </c>
+      <c r="B51" s="23">
         <v>3414</v>
       </c>
-      <c r="C51" s="35">
+      <c r="C51" s="25">
         <v>3804.8333333333335</v>
       </c>
-      <c r="D51" s="36"/>
+      <c r="D51" s="26"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B52" s="33">
+        <v>52</v>
+      </c>
+      <c r="B52" s="23">
         <v>2792</v>
       </c>
-      <c r="C52" s="35">
+      <c r="C52" s="25">
         <v>3816.625</v>
       </c>
-      <c r="D52" s="36"/>
+      <c r="D52" s="26"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B53" s="33">
+        <v>53</v>
+      </c>
+      <c r="B53" s="23">
         <v>3492</v>
       </c>
-      <c r="C53" s="35">
+      <c r="C53" s="25">
         <v>3830.9583333333335</v>
       </c>
-      <c r="D53" s="36"/>
+      <c r="D53" s="26"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B54" s="33">
+        <v>54</v>
+      </c>
+      <c r="B54" s="23">
         <v>3868</v>
       </c>
-      <c r="C54" s="35">
+      <c r="C54" s="25">
         <v>3853.2916666666665</v>
       </c>
-      <c r="D54" s="36"/>
+      <c r="D54" s="26"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B55" s="33">
+        <v>55</v>
+      </c>
+      <c r="B55" s="23">
         <v>4098</v>
       </c>
-      <c r="C55" s="35">
+      <c r="C55" s="25">
         <v>3875.5</v>
       </c>
-      <c r="D55" s="36"/>
+      <c r="D55" s="26"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B56" s="33">
+        <v>56</v>
+      </c>
+      <c r="B56" s="23">
         <v>4107</v>
       </c>
-      <c r="C56" s="35">
+      <c r="C56" s="25">
         <v>3899.8333333333335</v>
       </c>
-      <c r="D56" s="36"/>
+      <c r="D56" s="26"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B57" s="33">
+        <v>57</v>
+      </c>
+      <c r="B57" s="23">
         <v>4240</v>
       </c>
-      <c r="C57" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="D57" s="36"/>
+      <c r="C57" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D57" s="26"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B58" s="33">
+        <v>58</v>
+      </c>
+      <c r="B58" s="23">
         <v>4320</v>
       </c>
-      <c r="C58" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="D58" s="36"/>
+      <c r="C58" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D58" s="26"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B59" s="33">
+        <v>59</v>
+      </c>
+      <c r="B59" s="23">
         <v>4276</v>
       </c>
-      <c r="C59" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="D59" s="36"/>
+      <c r="C59" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D59" s="26"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B60" s="33">
+        <v>60</v>
+      </c>
+      <c r="B60" s="23">
         <v>4482</v>
       </c>
-      <c r="C60" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="D60" s="36"/>
+      <c r="C60" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D60" s="26"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B61" s="33">
+        <v>61</v>
+      </c>
+      <c r="B61" s="23">
         <v>3977</v>
       </c>
-      <c r="C61" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="D61" s="36"/>
+      <c r="C61" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D61" s="26"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B62" s="38">
+        <v>62</v>
+      </c>
+      <c r="B62" s="28">
         <v>3914</v>
       </c>
-      <c r="C62" s="38" t="s">
+      <c r="C62" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D62" s="26"/>
+    </row>
+    <row r="66" spans="1:14" ht="34.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="D62" s="36"/>
-    </row>
-    <row r="66" spans="1:14" ht="34.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="B66" s="29"/>
-      <c r="C66" s="29"/>
-      <c r="D66" s="29"/>
-      <c r="E66" s="29"/>
-      <c r="F66" s="29"/>
-      <c r="G66" s="29"/>
-      <c r="H66" s="29"/>
-      <c r="I66" s="29"/>
-      <c r="J66" s="29"/>
-      <c r="K66" s="29"/>
-      <c r="L66" s="29"/>
-      <c r="M66" s="29"/>
+      <c r="B66" s="37"/>
+      <c r="C66" s="37"/>
+      <c r="D66" s="37"/>
+      <c r="E66" s="37"/>
+      <c r="F66" s="37"/>
+      <c r="G66" s="37"/>
+      <c r="H66" s="37"/>
+      <c r="I66" s="37"/>
+      <c r="J66" s="37"/>
+      <c r="K66" s="37"/>
+      <c r="L66" s="37"/>
+      <c r="M66" s="37"/>
       <c r="N66" s="2"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B67" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B67" s="16" t="s">
+      <c r="C67" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="C67" s="16" t="s">
+      <c r="D67" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="D67" s="16" t="s">
+      <c r="E67" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="E67" s="16" t="s">
+      <c r="F67" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="F67" s="16" t="s">
+      <c r="G67" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="G67" s="16" t="s">
+      <c r="H67" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="H67" s="16" t="s">
+      <c r="I67" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="I67" s="16" t="s">
+      <c r="J67" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="J67" s="16" t="s">
+      <c r="K67" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="K67" s="16" t="s">
+      <c r="L67" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="L67" s="16" t="s">
+      <c r="M67" s="17" t="s">
         <v>75</v>
-      </c>
-      <c r="M67" s="17" t="s">
-        <v>76</v>
       </c>
       <c r="N67" s="5"/>
     </row>
@@ -4465,66 +4597,66 @@
       <c r="A68" s="22">
         <v>2017</v>
       </c>
-      <c r="B68" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="C68" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="D68" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="E68" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="F68" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="G68" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="H68" s="36"/>
-      <c r="I68" s="36"/>
-      <c r="J68" s="36"/>
-      <c r="K68" s="36"/>
-      <c r="L68" s="36"/>
-      <c r="M68" s="36"/>
+      <c r="B68" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C68" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D68" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E68" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="F68" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G68" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="H68" s="26"/>
+      <c r="I68" s="26"/>
+      <c r="J68" s="26"/>
+      <c r="K68" s="26"/>
+      <c r="L68" s="26"/>
+      <c r="M68" s="26"/>
       <c r="N68" s="6"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="22">
         <v>2018</v>
       </c>
-      <c r="B69" s="36"/>
-      <c r="C69" s="36"/>
-      <c r="D69" s="35">
+      <c r="B69" s="26"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="25">
         <v>-296.70833333333348</v>
       </c>
-      <c r="E69" s="35">
+      <c r="E69" s="25">
         <v>-334.16666666666652</v>
       </c>
-      <c r="F69" s="35">
+      <c r="F69" s="25">
         <v>135.25</v>
       </c>
-      <c r="G69" s="35">
+      <c r="G69" s="25">
         <v>221.58333333333348</v>
       </c>
-      <c r="H69" s="35">
+      <c r="H69" s="25">
         <v>270.91666666666652</v>
       </c>
-      <c r="I69" s="35">
+      <c r="I69" s="25">
         <v>219.79166666666652</v>
       </c>
-      <c r="J69" s="35">
+      <c r="J69" s="25">
         <v>319.54166666666652</v>
       </c>
-      <c r="K69" s="35">
+      <c r="K69" s="25">
         <v>395.83333333333348</v>
       </c>
-      <c r="L69" s="35">
+      <c r="L69" s="25">
         <v>-14.25</v>
       </c>
-      <c r="M69" s="37">
+      <c r="M69" s="27">
         <v>-79.458333333333485</v>
       </c>
       <c r="N69" s="6"/>
@@ -4533,40 +4665,40 @@
       <c r="A70" s="22">
         <v>2019</v>
       </c>
-      <c r="B70" s="35">
+      <c r="B70" s="25">
         <v>-308.70833333333348</v>
       </c>
-      <c r="C70" s="35">
+      <c r="C70" s="25">
         <v>-727.125</v>
       </c>
-      <c r="D70" s="35">
+      <c r="D70" s="25">
         <v>-311.08333333333348</v>
       </c>
-      <c r="E70" s="35">
+      <c r="E70" s="25">
         <v>-180.29166666666652</v>
       </c>
-      <c r="F70" s="35">
+      <c r="F70" s="25">
         <v>163</v>
       </c>
-      <c r="G70" s="35">
+      <c r="G70" s="25">
         <v>192.04166666666652</v>
       </c>
-      <c r="H70" s="35">
+      <c r="H70" s="25">
         <v>270.29166666666652</v>
       </c>
-      <c r="I70" s="35">
+      <c r="I70" s="25">
         <v>376</v>
       </c>
-      <c r="J70" s="35">
+      <c r="J70" s="25">
         <v>263.91666666666652</v>
       </c>
-      <c r="K70" s="35">
+      <c r="K70" s="25">
         <v>253.16666666666652</v>
       </c>
-      <c r="L70" s="35">
+      <c r="L70" s="25">
         <v>45.958333333333485</v>
       </c>
-      <c r="M70" s="37">
+      <c r="M70" s="27">
         <v>-20.208333333333485</v>
       </c>
       <c r="N70" s="6"/>
@@ -4575,143 +4707,143 @@
       <c r="A71" s="22">
         <v>2020</v>
       </c>
-      <c r="B71" s="35">
+      <c r="B71" s="25">
         <v>-399.29166666666652</v>
       </c>
-      <c r="C71" s="35">
+      <c r="C71" s="25">
         <v>-457.33333333333348</v>
       </c>
-      <c r="D71" s="35">
+      <c r="D71" s="25">
         <v>-534.66666666666652</v>
       </c>
-      <c r="E71" s="35">
+      <c r="E71" s="25">
         <v>-878.54166666666652</v>
       </c>
-      <c r="F71" s="35">
+      <c r="F71" s="25">
         <v>-135.29166666666652</v>
       </c>
-      <c r="G71" s="35">
+      <c r="G71" s="25">
         <v>489.16666666666652</v>
       </c>
-      <c r="H71" s="35">
+      <c r="H71" s="25">
         <v>528.125</v>
       </c>
-      <c r="I71" s="35">
+      <c r="I71" s="25">
         <v>631.29166666666652</v>
       </c>
-      <c r="J71" s="35">
+      <c r="J71" s="25">
         <v>462.33333333333348</v>
       </c>
-      <c r="K71" s="35">
+      <c r="K71" s="25">
         <v>496.875</v>
       </c>
-      <c r="L71" s="35">
+      <c r="L71" s="25">
         <v>-1.1666666666665151</v>
       </c>
-      <c r="M71" s="37">
+      <c r="M71" s="27">
         <v>-243.79166666666652</v>
       </c>
-      <c r="N71" s="23" t="s">
-        <v>77</v>
+      <c r="N71" s="38" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" s="22">
         <v>2021</v>
       </c>
-      <c r="B72" s="35">
+      <c r="B72" s="25">
         <v>-390.83333333333348</v>
       </c>
-      <c r="C72" s="35">
+      <c r="C72" s="25">
         <v>-1024.625</v>
       </c>
-      <c r="D72" s="35">
+      <c r="D72" s="25">
         <v>-338.95833333333348</v>
       </c>
-      <c r="E72" s="35">
+      <c r="E72" s="25">
         <v>14.708333333333485</v>
       </c>
-      <c r="F72" s="35">
+      <c r="F72" s="25">
         <v>222.5</v>
       </c>
-      <c r="G72" s="35">
+      <c r="G72" s="25">
         <v>207.16666666666652</v>
       </c>
-      <c r="H72" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="I72" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="J72" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="K72" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="L72" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="M72" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="N72" s="24"/>
+      <c r="H72" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="I72" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="J72" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="K72" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="L72" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="M72" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="N72" s="39"/>
     </row>
     <row r="73" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="B73" s="35">
+        <v>80</v>
+      </c>
+      <c r="B73" s="25">
         <v>-350.22916666666674</v>
       </c>
-      <c r="C73" s="35">
+      <c r="C73" s="25">
         <v>-695.78125</v>
       </c>
-      <c r="D73" s="35">
+      <c r="D73" s="25">
         <v>-370.35416666666674</v>
       </c>
-      <c r="E73" s="36"/>
-      <c r="F73" s="36"/>
-      <c r="G73" s="36"/>
-      <c r="H73" s="36"/>
-      <c r="I73" s="36"/>
-      <c r="J73" s="36"/>
-      <c r="K73" s="36"/>
-      <c r="L73" s="36"/>
-      <c r="M73" s="36"/>
+      <c r="E73" s="26"/>
+      <c r="F73" s="26"/>
+      <c r="G73" s="26"/>
+      <c r="H73" s="26"/>
+      <c r="I73" s="26"/>
+      <c r="J73" s="26"/>
+      <c r="K73" s="26"/>
+      <c r="L73" s="26"/>
+      <c r="M73" s="26"/>
       <c r="N73" s="7">
         <v>-5.0060763888889142</v>
       </c>
     </row>
     <row r="74" spans="1:14" ht="19.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="19"/>
-      <c r="B74" s="40">
+      <c r="B74" s="29">
         <v>-345.22309027777783</v>
       </c>
-      <c r="C74" s="36"/>
-      <c r="D74" s="36"/>
-      <c r="E74" s="36"/>
-      <c r="F74" s="36"/>
-      <c r="G74" s="36"/>
-      <c r="H74" s="36"/>
-      <c r="I74" s="36"/>
-      <c r="J74" s="36"/>
-      <c r="K74" s="36"/>
-      <c r="L74" s="36"/>
-      <c r="M74" s="36"/>
+      <c r="C74" s="26"/>
+      <c r="D74" s="26"/>
+      <c r="E74" s="26"/>
+      <c r="F74" s="26"/>
+      <c r="G74" s="26"/>
+      <c r="H74" s="26"/>
+      <c r="I74" s="26"/>
+      <c r="J74" s="26"/>
+      <c r="K74" s="26"/>
+      <c r="L74" s="26"/>
+      <c r="M74" s="26"/>
       <c r="N74" s="8"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.35"/>
     <row r="78" spans="1:14" ht="43.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A78" s="25" t="s">
+      <c r="A78" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="B78" s="26"/>
-      <c r="C78" s="26"/>
-      <c r="D78" s="26"/>
-      <c r="E78" s="26"/>
-      <c r="F78" s="26"/>
-      <c r="G78" s="27"/>
+      <c r="B78" s="31"/>
+      <c r="C78" s="31"/>
+      <c r="D78" s="31"/>
+      <c r="E78" s="31"/>
+      <c r="F78" s="31"/>
+      <c r="G78" s="32"/>
     </row>
     <row r="79" spans="1:14" ht="37.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="12" t="s">
@@ -4723,625 +4855,625 @@
       <c r="C79" s="14"/>
       <c r="D79" s="14"/>
       <c r="E79" s="14"/>
-      <c r="F79" s="14" t="s">
+      <c r="F79" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G79" s="15" t="s">
         <v>2</v>
-      </c>
-      <c r="G79" s="15" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B80" s="33">
+        <v>3</v>
+      </c>
+      <c r="B80" s="23">
         <f>B3</f>
         <v>3034</v>
       </c>
-      <c r="C80" s="33" t="str">
+      <c r="C80" s="23" t="str">
         <f t="shared" ref="C80:D80" si="0">C3</f>
         <v>NA</v>
       </c>
-      <c r="D80" s="33" t="str">
-        <f t="shared" si="0"/>
+      <c r="D80" s="24" t="str">
+        <f>IF(LEN(D3)&gt;0,D3,"")</f>
         <v>NA</v>
       </c>
-      <c r="E80" s="36"/>
-      <c r="F80" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="G80" s="36"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G80" s="26"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B81" s="33">
+        <v>4</v>
+      </c>
+      <c r="B81" s="23">
         <f t="shared" ref="B81:D96" si="1">B4</f>
         <v>2748</v>
       </c>
-      <c r="C81" s="33" t="str">
+      <c r="C81" s="23" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
-      <c r="D81" s="37" t="str">
+      <c r="D81" s="24" t="str">
+        <f t="shared" ref="D81:D139" si="2">IF(LEN(D4)&gt;0,D4,"")</f>
+        <v>NA</v>
+      </c>
+      <c r="E81" s="26"/>
+      <c r="F81" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G81" s="26"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A82" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B82" s="23">
+        <f t="shared" si="1"/>
+        <v>3164</v>
+      </c>
+      <c r="C82" s="23" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
-      <c r="E81" s="36"/>
-      <c r="F81" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="G81" s="36"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A82" s="3" t="s">
+      <c r="D82" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>NA</v>
+      </c>
+      <c r="E82" s="26"/>
+      <c r="F82" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G82" s="26"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A83" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B82" s="33">
+      <c r="B83" s="23">
         <f t="shared" si="1"/>
-        <v>3164</v>
-      </c>
-      <c r="C82" s="33" t="str">
+        <v>3238</v>
+      </c>
+      <c r="C83" s="23" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
-      <c r="D82" s="37" t="str">
+      <c r="D83" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>NA</v>
+      </c>
+      <c r="E83" s="26"/>
+      <c r="F83" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G83" s="26"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A84" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B84" s="23">
+        <f t="shared" si="1"/>
+        <v>3416</v>
+      </c>
+      <c r="C84" s="23" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
-      <c r="E82" s="36"/>
-      <c r="F82" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="G82" s="36"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A83" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B83" s="33">
+      <c r="D84" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>NA</v>
+      </c>
+      <c r="E84" s="26"/>
+      <c r="F84" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G84" s="26"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A85" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B85" s="23">
         <f t="shared" si="1"/>
-        <v>3238</v>
-      </c>
-      <c r="C83" s="33" t="str">
+        <v>3492</v>
+      </c>
+      <c r="C85" s="23" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
-      <c r="D83" s="37" t="str">
-        <f t="shared" si="1"/>
+      <c r="D85" s="24" t="str">
+        <f t="shared" si="2"/>
         <v>NA</v>
       </c>
-      <c r="E83" s="36"/>
-      <c r="F83" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="G83" s="36"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A84" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B84" s="33">
-        <f t="shared" si="1"/>
-        <v>3416</v>
-      </c>
-      <c r="C84" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>NA</v>
-      </c>
-      <c r="D84" s="37" t="str">
-        <f t="shared" si="1"/>
-        <v>NA</v>
-      </c>
-      <c r="E84" s="36"/>
-      <c r="F84" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="G84" s="36"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A85" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B85" s="33">
-        <f t="shared" si="1"/>
-        <v>3492</v>
-      </c>
-      <c r="C85" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>NA</v>
-      </c>
-      <c r="D85" s="37" t="str">
-        <f t="shared" si="1"/>
-        <v>NA</v>
-      </c>
-      <c r="E85" s="36"/>
-      <c r="F85" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="G85" s="36"/>
+      <c r="E85" s="26"/>
+      <c r="F85" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G85" s="26"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B86" s="33">
+        <v>9</v>
+      </c>
+      <c r="B86" s="23">
         <f t="shared" si="1"/>
         <v>3730</v>
       </c>
-      <c r="C86" s="35">
+      <c r="C86" s="25">
         <f t="shared" si="1"/>
         <v>3351.5833333333335</v>
       </c>
-      <c r="D86" s="37">
-        <f t="shared" si="1"/>
+      <c r="D86" s="27">
+        <f t="shared" si="2"/>
         <v>378.41666666666652</v>
       </c>
-      <c r="E86" s="36"/>
-      <c r="F86" s="36"/>
-      <c r="G86" s="36"/>
+      <c r="E86" s="26"/>
+      <c r="F86" s="26"/>
+      <c r="G86" s="26"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B87" s="33">
+        <v>10</v>
+      </c>
+      <c r="B87" s="23">
         <f t="shared" si="1"/>
         <v>3409</v>
       </c>
-      <c r="C87" s="35">
+      <c r="C87" s="25">
         <f t="shared" si="1"/>
         <v>3350</v>
       </c>
-      <c r="D87" s="37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E87" s="36"/>
-      <c r="F87" s="36"/>
-      <c r="G87" s="36"/>
+      <c r="D87" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E87" s="26"/>
+      <c r="F87" s="26"/>
+      <c r="G87" s="26"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B88" s="33">
+        <v>11</v>
+      </c>
+      <c r="B88" s="23">
         <f t="shared" si="1"/>
         <v>3572</v>
       </c>
-      <c r="C88" s="35">
+      <c r="C88" s="25">
         <f t="shared" si="1"/>
         <v>3343.2083333333335</v>
       </c>
-      <c r="D88" s="37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E88" s="36"/>
-      <c r="F88" s="36"/>
-      <c r="G88" s="36"/>
+      <c r="D88" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E88" s="26"/>
+      <c r="F88" s="26"/>
+      <c r="G88" s="26"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B89" s="33">
+        <v>12</v>
+      </c>
+      <c r="B89" s="23">
         <f t="shared" si="1"/>
         <v>3629</v>
       </c>
-      <c r="C89" s="35">
+      <c r="C89" s="25">
         <f t="shared" si="1"/>
         <v>3326.2083333333335</v>
       </c>
-      <c r="D89" s="37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E89" s="36"/>
-      <c r="F89" s="36"/>
-      <c r="G89" s="36"/>
+      <c r="D89" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E89" s="26"/>
+      <c r="F89" s="26"/>
+      <c r="G89" s="26"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B90" s="33">
+        <v>13</v>
+      </c>
+      <c r="B90" s="23">
         <f t="shared" si="1"/>
         <v>3408</v>
       </c>
-      <c r="C90" s="35">
+      <c r="C90" s="25">
         <f t="shared" si="1"/>
         <v>3316.5416666666665</v>
       </c>
-      <c r="D90" s="37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E90" s="36"/>
-      <c r="F90" s="36"/>
-      <c r="G90" s="36"/>
+      <c r="D90" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E90" s="26"/>
+      <c r="F90" s="26"/>
+      <c r="G90" s="26"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" s="33">
+        <v>14</v>
+      </c>
+      <c r="B91" s="23">
         <f t="shared" si="1"/>
         <v>3391</v>
       </c>
-      <c r="C91" s="35">
+      <c r="C91" s="25">
         <f t="shared" si="1"/>
         <v>3318.5833333333335</v>
       </c>
-      <c r="D91" s="37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E91" s="36"/>
-      <c r="F91" s="36"/>
-      <c r="G91" s="36"/>
+      <c r="D91" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E91" s="26"/>
+      <c r="F91" s="26"/>
+      <c r="G91" s="26"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B92" s="33">
+        <v>15</v>
+      </c>
+      <c r="B92" s="23">
         <f t="shared" si="1"/>
         <v>3010</v>
       </c>
-      <c r="C92" s="35">
+      <c r="C92" s="25">
         <f t="shared" si="1"/>
         <v>3312.0833333333335</v>
       </c>
-      <c r="D92" s="37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E92" s="36"/>
-      <c r="F92" s="36"/>
-      <c r="G92" s="36"/>
+      <c r="D92" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E92" s="26"/>
+      <c r="F92" s="26"/>
+      <c r="G92" s="26"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B93" s="33">
+        <v>16</v>
+      </c>
+      <c r="B93" s="23">
         <f t="shared" si="1"/>
         <v>2734</v>
       </c>
-      <c r="C93" s="35">
+      <c r="C93" s="25">
         <f t="shared" si="1"/>
         <v>3308.0416666666665</v>
       </c>
-      <c r="D93" s="37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E93" s="36"/>
-      <c r="F93" s="36"/>
-      <c r="G93" s="36"/>
+      <c r="D93" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E93" s="26"/>
+      <c r="F93" s="26"/>
+      <c r="G93" s="26"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B94" s="33">
+        <v>17</v>
+      </c>
+      <c r="B94" s="23">
         <f t="shared" si="1"/>
         <v>3015</v>
       </c>
-      <c r="C94" s="35">
+      <c r="C94" s="25">
         <f t="shared" si="1"/>
         <v>3311.7083333333335</v>
       </c>
-      <c r="D94" s="37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E94" s="36"/>
-      <c r="F94" s="36"/>
-      <c r="G94" s="36"/>
+      <c r="D94" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E94" s="26"/>
+      <c r="F94" s="26"/>
+      <c r="G94" s="26"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B95" s="33">
+        <v>18</v>
+      </c>
+      <c r="B95" s="23">
         <f t="shared" si="1"/>
         <v>2979</v>
       </c>
-      <c r="C95" s="35">
+      <c r="C95" s="25">
         <f t="shared" si="1"/>
         <v>3313.1666666666665</v>
       </c>
-      <c r="D95" s="37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E95" s="36"/>
-      <c r="F95" s="36"/>
-      <c r="G95" s="36"/>
+      <c r="D95" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E95" s="26"/>
+      <c r="F95" s="26"/>
+      <c r="G95" s="26"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B96" s="33">
+        <v>19</v>
+      </c>
+      <c r="B96" s="23">
         <f t="shared" si="1"/>
         <v>3443</v>
       </c>
-      <c r="C96" s="35">
+      <c r="C96" s="25">
         <f t="shared" si="1"/>
         <v>3307.75</v>
       </c>
-      <c r="D96" s="37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E96" s="36"/>
-      <c r="F96" s="36"/>
-      <c r="G96" s="36"/>
+      <c r="D96" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E96" s="26"/>
+      <c r="F96" s="26"/>
+      <c r="G96" s="26"/>
       <c r="H96" s="1"/>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B97" s="33">
-        <f t="shared" ref="B97:D112" si="2">B20</f>
+        <v>20</v>
+      </c>
+      <c r="B97" s="23">
+        <f t="shared" ref="B97:D112" si="3">B20</f>
         <v>3514</v>
       </c>
-      <c r="C97" s="35">
+      <c r="C97" s="25">
+        <f t="shared" si="3"/>
+        <v>3292.4166666666665</v>
+      </c>
+      <c r="D97" s="26" t="str">
         <f t="shared" si="2"/>
-        <v>3292.4166666666665</v>
-      </c>
-      <c r="D97" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E97" s="36"/>
-      <c r="F97" s="36"/>
-      <c r="G97" s="36"/>
+        <v/>
+      </c>
+      <c r="E97" s="26"/>
+      <c r="F97" s="26"/>
+      <c r="G97" s="26"/>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B98" s="33">
+        <v>21</v>
+      </c>
+      <c r="B98" s="23">
+        <f t="shared" si="3"/>
+        <v>3552</v>
+      </c>
+      <c r="C98" s="25">
+        <f t="shared" si="3"/>
+        <v>3281.0833333333335</v>
+      </c>
+      <c r="D98" s="26" t="str">
         <f t="shared" si="2"/>
-        <v>3552</v>
-      </c>
-      <c r="C98" s="35">
-        <f t="shared" si="2"/>
-        <v>3281.0833333333335</v>
-      </c>
-      <c r="D98" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E98" s="36"/>
-      <c r="F98" s="36"/>
-      <c r="G98" s="36"/>
+        <v/>
+      </c>
+      <c r="E98" s="26"/>
+      <c r="F98" s="26"/>
+      <c r="G98" s="26"/>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B99" s="33">
+        <v>22</v>
+      </c>
+      <c r="B99" s="23">
+        <f t="shared" si="3"/>
+        <v>3490</v>
+      </c>
+      <c r="C99" s="25">
+        <f t="shared" si="3"/>
+        <v>3270.2083333333335</v>
+      </c>
+      <c r="D99" s="26" t="str">
         <f t="shared" si="2"/>
-        <v>3490</v>
-      </c>
-      <c r="C99" s="35">
-        <f t="shared" si="2"/>
-        <v>3270.2083333333335</v>
-      </c>
-      <c r="D99" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E99" s="36"/>
-      <c r="F99" s="36"/>
-      <c r="G99" s="36"/>
+        <v/>
+      </c>
+      <c r="E99" s="26"/>
+      <c r="F99" s="26"/>
+      <c r="G99" s="26"/>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A100" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B100" s="33">
+        <v>23</v>
+      </c>
+      <c r="B100" s="23">
+        <f t="shared" si="3"/>
+        <v>3579</v>
+      </c>
+      <c r="C100" s="25">
+        <f t="shared" si="3"/>
+        <v>3259.4583333333335</v>
+      </c>
+      <c r="D100" s="26" t="str">
         <f t="shared" si="2"/>
-        <v>3579</v>
-      </c>
-      <c r="C100" s="35">
-        <f t="shared" si="2"/>
-        <v>3259.4583333333335</v>
-      </c>
-      <c r="D100" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E100" s="36"/>
-      <c r="F100" s="36"/>
-      <c r="G100" s="36"/>
+        <v/>
+      </c>
+      <c r="E100" s="26"/>
+      <c r="F100" s="26"/>
+      <c r="G100" s="26"/>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A101" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B101" s="33">
+        <v>24</v>
+      </c>
+      <c r="B101" s="23">
+        <f t="shared" si="3"/>
+        <v>3657</v>
+      </c>
+      <c r="C101" s="25">
+        <f t="shared" si="3"/>
+        <v>3261.1666666666665</v>
+      </c>
+      <c r="D101" s="26" t="str">
         <f t="shared" si="2"/>
-        <v>3657</v>
-      </c>
-      <c r="C101" s="35">
-        <f t="shared" si="2"/>
-        <v>3261.1666666666665</v>
-      </c>
-      <c r="D101" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E101" s="36"/>
-      <c r="F101" s="36"/>
-      <c r="G101" s="36"/>
+        <v/>
+      </c>
+      <c r="E101" s="26"/>
+      <c r="F101" s="26"/>
+      <c r="G101" s="26"/>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A102" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B102" s="33">
+        <v>25</v>
+      </c>
+      <c r="B102" s="23">
+        <f t="shared" si="3"/>
+        <v>3250</v>
+      </c>
+      <c r="C102" s="25">
+        <f t="shared" si="3"/>
+        <v>3264.25</v>
+      </c>
+      <c r="D102" s="26" t="str">
         <f t="shared" si="2"/>
-        <v>3250</v>
-      </c>
-      <c r="C102" s="35">
-        <f t="shared" si="2"/>
-        <v>3264.25</v>
-      </c>
-      <c r="D102" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E102" s="36"/>
-      <c r="F102" s="36"/>
-      <c r="G102" s="36"/>
+        <v/>
+      </c>
+      <c r="E102" s="26"/>
+      <c r="F102" s="26"/>
+      <c r="G102" s="26"/>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B103" s="33">
+        <v>26</v>
+      </c>
+      <c r="B103" s="23">
+        <f t="shared" si="3"/>
+        <v>3181</v>
+      </c>
+      <c r="C103" s="25">
+        <f t="shared" si="3"/>
+        <v>3260.4583333333335</v>
+      </c>
+      <c r="D103" s="26" t="str">
         <f t="shared" si="2"/>
-        <v>3181</v>
-      </c>
-      <c r="C103" s="35">
-        <f t="shared" si="2"/>
-        <v>3260.4583333333335</v>
-      </c>
-      <c r="D103" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E103" s="36"/>
-      <c r="F103" s="36"/>
-      <c r="G103" s="36"/>
+        <v/>
+      </c>
+      <c r="E103" s="26"/>
+      <c r="F103" s="26"/>
+      <c r="G103" s="26"/>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A104" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B104" s="33">
+        <v>27</v>
+      </c>
+      <c r="B104" s="23">
+        <f t="shared" si="3"/>
+        <v>2948</v>
+      </c>
+      <c r="C104" s="25">
+        <f t="shared" si="3"/>
+        <v>3256.7083333333335</v>
+      </c>
+      <c r="D104" s="26" t="str">
         <f t="shared" si="2"/>
-        <v>2948</v>
-      </c>
-      <c r="C104" s="35">
-        <f t="shared" si="2"/>
-        <v>3256.7083333333335</v>
-      </c>
-      <c r="D104" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E104" s="36"/>
-      <c r="F104" s="36"/>
-      <c r="G104" s="36"/>
+        <v/>
+      </c>
+      <c r="E104" s="26"/>
+      <c r="F104" s="26"/>
+      <c r="G104" s="26"/>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B105" s="33">
+        <v>28</v>
+      </c>
+      <c r="B105" s="23">
+        <f t="shared" si="3"/>
+        <v>2535</v>
+      </c>
+      <c r="C105" s="25">
+        <f t="shared" si="3"/>
+        <v>3262.125</v>
+      </c>
+      <c r="D105" s="26" t="str">
         <f t="shared" si="2"/>
-        <v>2535</v>
-      </c>
-      <c r="C105" s="35">
-        <f t="shared" si="2"/>
-        <v>3262.125</v>
-      </c>
-      <c r="D105" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E105" s="36"/>
-      <c r="F105" s="36"/>
-      <c r="G105" s="36"/>
+        <v/>
+      </c>
+      <c r="E105" s="26"/>
+      <c r="F105" s="26"/>
+      <c r="G105" s="26"/>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A106" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B106" s="33">
+        <v>29</v>
+      </c>
+      <c r="B106" s="23">
+        <f t="shared" si="3"/>
+        <v>2956</v>
+      </c>
+      <c r="C106" s="25">
+        <f t="shared" si="3"/>
+        <v>3267.0833333333335</v>
+      </c>
+      <c r="D106" s="26" t="str">
         <f t="shared" si="2"/>
-        <v>2956</v>
-      </c>
-      <c r="C106" s="35">
-        <f t="shared" si="2"/>
-        <v>3267.0833333333335</v>
-      </c>
-      <c r="D106" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E106" s="36"/>
-      <c r="F106" s="36"/>
-      <c r="G106" s="36"/>
+        <v/>
+      </c>
+      <c r="E106" s="26"/>
+      <c r="F106" s="26"/>
+      <c r="G106" s="26"/>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B107" s="33">
+        <v>30</v>
+      </c>
+      <c r="B107" s="23">
+        <f t="shared" si="3"/>
+        <v>3079</v>
+      </c>
+      <c r="C107" s="25">
+        <f t="shared" si="3"/>
+        <v>3259.2916666666665</v>
+      </c>
+      <c r="D107" s="26" t="str">
         <f t="shared" si="2"/>
-        <v>3079</v>
-      </c>
-      <c r="C107" s="35">
-        <f t="shared" si="2"/>
-        <v>3259.2916666666665</v>
-      </c>
-      <c r="D107" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E107" s="36"/>
-      <c r="F107" s="36"/>
-      <c r="G107" s="36"/>
+        <v/>
+      </c>
+      <c r="E107" s="26"/>
+      <c r="F107" s="26"/>
+      <c r="G107" s="26"/>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A108" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B108" s="33">
+        <v>31</v>
+      </c>
+      <c r="B108" s="23">
+        <f t="shared" si="3"/>
+        <v>3417</v>
+      </c>
+      <c r="C108" s="25">
+        <f t="shared" si="3"/>
+        <v>3254</v>
+      </c>
+      <c r="D108" s="26" t="str">
         <f t="shared" si="2"/>
-        <v>3417</v>
-      </c>
-      <c r="C108" s="35">
-        <f t="shared" si="2"/>
-        <v>3254</v>
-      </c>
-      <c r="D108" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E108" s="36"/>
-      <c r="F108" s="36"/>
-      <c r="G108" s="36"/>
+        <v/>
+      </c>
+      <c r="E108" s="26"/>
+      <c r="F108" s="26"/>
+      <c r="G108" s="26"/>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A109" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B109" s="33">
+        <v>32</v>
+      </c>
+      <c r="B109" s="23">
+        <f t="shared" si="3"/>
+        <v>3449</v>
+      </c>
+      <c r="C109" s="25">
+        <f t="shared" si="3"/>
+        <v>3256.9583333333335</v>
+      </c>
+      <c r="D109" s="26" t="str">
         <f t="shared" si="2"/>
-        <v>3449</v>
-      </c>
-      <c r="C109" s="35">
-        <f t="shared" si="2"/>
-        <v>3256.9583333333335</v>
-      </c>
-      <c r="D109" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E109" s="36"/>
-      <c r="F109" s="36"/>
-      <c r="G109" s="36"/>
+        <v/>
+      </c>
+      <c r="E109" s="26"/>
+      <c r="F109" s="26"/>
+      <c r="G109" s="26"/>
       <c r="H109" s="1"/>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
@@ -5351,23 +5483,23 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B110" s="33">
+        <v>33</v>
+      </c>
+      <c r="B110" s="23">
+        <f t="shared" si="3"/>
+        <v>3527</v>
+      </c>
+      <c r="C110" s="25">
+        <f t="shared" si="3"/>
+        <v>3256.7083333333335</v>
+      </c>
+      <c r="D110" s="26" t="str">
         <f t="shared" si="2"/>
-        <v>3527</v>
-      </c>
-      <c r="C110" s="35">
-        <f t="shared" si="2"/>
-        <v>3256.7083333333335</v>
-      </c>
-      <c r="D110" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E110" s="36"/>
-      <c r="F110" s="36"/>
-      <c r="G110" s="36"/>
+        <v/>
+      </c>
+      <c r="E110" s="26"/>
+      <c r="F110" s="26"/>
+      <c r="G110" s="26"/>
       <c r="H110" s="1"/>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
@@ -5377,23 +5509,23 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B111" s="33">
+        <v>34</v>
+      </c>
+      <c r="B111" s="23">
+        <f t="shared" si="3"/>
+        <v>3645</v>
+      </c>
+      <c r="C111" s="25">
+        <f t="shared" si="3"/>
+        <v>3269</v>
+      </c>
+      <c r="D111" s="26" t="str">
         <f t="shared" si="2"/>
-        <v>3645</v>
-      </c>
-      <c r="C111" s="35">
-        <f t="shared" si="2"/>
-        <v>3269</v>
-      </c>
-      <c r="D111" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E111" s="36"/>
-      <c r="F111" s="36"/>
-      <c r="G111" s="36"/>
+        <v/>
+      </c>
+      <c r="E111" s="26"/>
+      <c r="F111" s="26"/>
+      <c r="G111" s="26"/>
       <c r="H111" s="1"/>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
@@ -5403,23 +5535,23 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A112" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B112" s="33">
+        <v>35</v>
+      </c>
+      <c r="B112" s="23">
+        <f t="shared" si="3"/>
+        <v>3543</v>
+      </c>
+      <c r="C112" s="25">
+        <f t="shared" si="3"/>
+        <v>3279.0833333333335</v>
+      </c>
+      <c r="D112" s="26" t="str">
         <f t="shared" si="2"/>
-        <v>3543</v>
-      </c>
-      <c r="C112" s="35">
-        <f t="shared" si="2"/>
-        <v>3279.0833333333335</v>
-      </c>
-      <c r="D112" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E112" s="36"/>
-      <c r="F112" s="36"/>
-      <c r="G112" s="36"/>
+        <v/>
+      </c>
+      <c r="E112" s="26"/>
+      <c r="F112" s="26"/>
+      <c r="G112" s="26"/>
       <c r="H112" s="1"/>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
@@ -5429,43 +5561,43 @@
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A113" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B113" s="33">
-        <f t="shared" ref="B113:D128" si="3">B36</f>
+        <v>36</v>
+      </c>
+      <c r="B113" s="23">
+        <f t="shared" ref="B113:D128" si="4">B36</f>
         <v>3506</v>
       </c>
-      <c r="C113" s="35">
-        <f t="shared" si="3"/>
+      <c r="C113" s="25">
+        <f t="shared" si="4"/>
         <v>3252.8333333333335</v>
       </c>
-      <c r="D113" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E113" s="36"/>
-      <c r="F113" s="36"/>
-      <c r="G113" s="36"/>
+      <c r="D113" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E113" s="26"/>
+      <c r="F113" s="26"/>
+      <c r="G113" s="26"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A114" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B114" s="33">
-        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B114" s="23">
+        <f t="shared" si="4"/>
         <v>3274</v>
       </c>
-      <c r="C114" s="35">
-        <f t="shared" si="3"/>
+      <c r="C114" s="25">
+        <f t="shared" si="4"/>
         <v>3228.0416666666665</v>
       </c>
-      <c r="D114" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E114" s="36"/>
-      <c r="F114" s="36"/>
-      <c r="G114" s="36"/>
+      <c r="D114" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E114" s="26"/>
+      <c r="F114" s="26"/>
+      <c r="G114" s="26"/>
       <c r="H114" s="1"/>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -5475,23 +5607,23 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A115" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B115" s="33">
-        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B115" s="23">
+        <f t="shared" si="4"/>
         <v>3228</v>
       </c>
-      <c r="C115" s="35">
-        <f t="shared" si="3"/>
+      <c r="C115" s="25">
+        <f t="shared" si="4"/>
         <v>3248.2083333333335</v>
       </c>
-      <c r="D115" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E115" s="36"/>
-      <c r="F115" s="36"/>
-      <c r="G115" s="36"/>
+      <c r="D115" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E115" s="26"/>
+      <c r="F115" s="26"/>
+      <c r="G115" s="26"/>
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -5502,483 +5634,483 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A116" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B116" s="33">
-        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B116" s="23">
+        <f t="shared" si="4"/>
         <v>2895</v>
       </c>
-      <c r="C116" s="35">
-        <f t="shared" si="3"/>
+      <c r="C116" s="25">
+        <f t="shared" si="4"/>
         <v>3294.2916666666665</v>
       </c>
-      <c r="D116" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E116" s="36"/>
-      <c r="F116" s="36"/>
-      <c r="G116" s="36"/>
+      <c r="D116" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E116" s="26"/>
+      <c r="F116" s="26"/>
+      <c r="G116" s="26"/>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A117" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B117" s="33">
-        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B117" s="23">
+        <f t="shared" si="4"/>
         <v>2883</v>
       </c>
-      <c r="C117" s="35">
-        <f t="shared" si="3"/>
+      <c r="C117" s="25">
+        <f t="shared" si="4"/>
         <v>3340.3333333333335</v>
       </c>
-      <c r="D117" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E117" s="36"/>
-      <c r="F117" s="36"/>
-      <c r="G117" s="36"/>
+      <c r="D117" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E117" s="26"/>
+      <c r="F117" s="26"/>
+      <c r="G117" s="26"/>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A118" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B118" s="33">
-        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B118" s="23">
+        <f t="shared" si="4"/>
         <v>2850</v>
       </c>
-      <c r="C118" s="35">
-        <f t="shared" si="3"/>
+      <c r="C118" s="25">
+        <f t="shared" si="4"/>
         <v>3384.6666666666665</v>
       </c>
-      <c r="D118" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E118" s="36"/>
-      <c r="F118" s="36"/>
-      <c r="G118" s="36"/>
+      <c r="D118" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E118" s="26"/>
+      <c r="F118" s="26"/>
+      <c r="G118" s="26"/>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A119" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B119" s="33">
-        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B119" s="23">
+        <f t="shared" si="4"/>
         <v>2555</v>
       </c>
-      <c r="C119" s="35">
-        <f t="shared" si="3"/>
+      <c r="C119" s="25">
+        <f t="shared" si="4"/>
         <v>3433.5416666666665</v>
       </c>
-      <c r="D119" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E119" s="36"/>
-      <c r="F119" s="36"/>
-      <c r="G119" s="36"/>
+      <c r="D119" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E119" s="26"/>
+      <c r="F119" s="26"/>
+      <c r="G119" s="26"/>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A120" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B120" s="33">
-        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B120" s="23">
+        <f t="shared" si="4"/>
         <v>3346</v>
       </c>
-      <c r="C120" s="35">
-        <f t="shared" si="3"/>
+      <c r="C120" s="25">
+        <f t="shared" si="4"/>
         <v>3481.2916666666665</v>
       </c>
-      <c r="D120" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E120" s="36"/>
-      <c r="F120" s="36"/>
-      <c r="G120" s="36"/>
+      <c r="D120" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E120" s="26"/>
+      <c r="F120" s="26"/>
+      <c r="G120" s="26"/>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A121" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B121" s="33">
-        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B121" s="23">
+        <f t="shared" si="4"/>
         <v>4004</v>
       </c>
-      <c r="C121" s="35">
-        <f t="shared" si="3"/>
+      <c r="C121" s="25">
+        <f t="shared" si="4"/>
         <v>3514.8333333333335</v>
       </c>
-      <c r="D121" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E121" s="36"/>
-      <c r="F121" s="36"/>
-      <c r="G121" s="36"/>
+      <c r="D121" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E121" s="26"/>
+      <c r="F121" s="26"/>
+      <c r="G121" s="26"/>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A122" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B122" s="33">
-        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B122" s="23">
+        <f t="shared" si="4"/>
         <v>4078</v>
       </c>
-      <c r="C122" s="35">
-        <f t="shared" si="3"/>
+      <c r="C122" s="25">
+        <f t="shared" si="4"/>
         <v>3549.875</v>
       </c>
-      <c r="D122" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E122" s="36"/>
-      <c r="F122" s="36"/>
-      <c r="G122" s="36"/>
+      <c r="D122" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E122" s="26"/>
+      <c r="F122" s="26"/>
+      <c r="G122" s="26"/>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A123" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B123" s="33">
-        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B123" s="23">
+        <f t="shared" si="4"/>
         <v>4199</v>
       </c>
-      <c r="C123" s="35">
-        <f t="shared" si="3"/>
+      <c r="C123" s="25">
+        <f t="shared" si="4"/>
         <v>3567.7083333333335</v>
       </c>
-      <c r="D123" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E123" s="36"/>
-      <c r="F123" s="36"/>
-      <c r="G123" s="36"/>
+      <c r="D123" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E123" s="26"/>
+      <c r="F123" s="26"/>
+      <c r="G123" s="26"/>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A124" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B124" s="33">
-        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B124" s="23">
+        <f t="shared" si="4"/>
         <v>4053</v>
       </c>
-      <c r="C124" s="35">
-        <f t="shared" si="3"/>
+      <c r="C124" s="25">
+        <f t="shared" si="4"/>
         <v>3590.6666666666665</v>
       </c>
-      <c r="D124" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E124" s="36"/>
-      <c r="F124" s="36"/>
-      <c r="G124" s="36"/>
+      <c r="D124" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E124" s="26"/>
+      <c r="F124" s="26"/>
+      <c r="G124" s="26"/>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A125" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B125" s="33">
-        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B125" s="23">
+        <f t="shared" si="4"/>
         <v>4169</v>
       </c>
-      <c r="C125" s="35">
-        <f t="shared" si="3"/>
+      <c r="C125" s="25">
+        <f t="shared" si="4"/>
         <v>3672.125</v>
       </c>
-      <c r="D125" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E125" s="36"/>
-      <c r="F125" s="36"/>
-      <c r="G125" s="36"/>
+      <c r="D125" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E125" s="26"/>
+      <c r="F125" s="26"/>
+      <c r="G125" s="26"/>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A126" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B126" s="33">
-        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B126" s="23">
+        <f t="shared" si="4"/>
         <v>3757</v>
       </c>
-      <c r="C126" s="35">
-        <f t="shared" si="3"/>
+      <c r="C126" s="25">
+        <f t="shared" si="4"/>
         <v>3758.1666666666665</v>
       </c>
-      <c r="D126" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E126" s="36"/>
-      <c r="F126" s="36"/>
-      <c r="G126" s="36"/>
+      <c r="D126" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E126" s="26"/>
+      <c r="F126" s="26"/>
+      <c r="G126" s="26"/>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A127" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B127" s="33">
-        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B127" s="23">
+        <f t="shared" si="4"/>
         <v>3550</v>
       </c>
-      <c r="C127" s="35">
-        <f t="shared" si="3"/>
+      <c r="C127" s="25">
+        <f t="shared" si="4"/>
         <v>3793.7916666666665</v>
       </c>
-      <c r="D127" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E127" s="36"/>
-      <c r="F127" s="36"/>
-      <c r="G127" s="36"/>
+      <c r="D127" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E127" s="26"/>
+      <c r="F127" s="26"/>
+      <c r="G127" s="26"/>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A128" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B128" s="33">
-        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B128" s="23">
+        <f t="shared" si="4"/>
         <v>3414</v>
       </c>
-      <c r="C128" s="35">
-        <f t="shared" si="3"/>
+      <c r="C128" s="25">
+        <f t="shared" si="4"/>
         <v>3804.8333333333335</v>
       </c>
-      <c r="D128" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E128" s="36"/>
-      <c r="F128" s="36"/>
-      <c r="G128" s="36"/>
+      <c r="D128" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E128" s="26"/>
+      <c r="F128" s="26"/>
+      <c r="G128" s="26"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B129" s="33">
-        <f t="shared" ref="B129:D139" si="4">B52</f>
+        <v>52</v>
+      </c>
+      <c r="B129" s="23">
+        <f t="shared" ref="B129:D139" si="5">B52</f>
         <v>2792</v>
       </c>
-      <c r="C129" s="35">
-        <f t="shared" si="4"/>
+      <c r="C129" s="25">
+        <f t="shared" si="5"/>
         <v>3816.625</v>
       </c>
-      <c r="D129" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E129" s="36"/>
-      <c r="F129" s="36"/>
-      <c r="G129" s="36"/>
+      <c r="D129" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E129" s="26"/>
+      <c r="F129" s="26"/>
+      <c r="G129" s="26"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B130" s="33">
-        <f t="shared" si="4"/>
+        <v>53</v>
+      </c>
+      <c r="B130" s="23">
+        <f t="shared" si="5"/>
         <v>3492</v>
       </c>
-      <c r="C130" s="35">
-        <f t="shared" si="4"/>
+      <c r="C130" s="25">
+        <f t="shared" si="5"/>
         <v>3830.9583333333335</v>
       </c>
-      <c r="D130" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E130" s="36"/>
-      <c r="F130" s="36"/>
-      <c r="G130" s="36"/>
+      <c r="D130" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E130" s="26"/>
+      <c r="F130" s="26"/>
+      <c r="G130" s="26"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B131" s="33">
-        <f t="shared" si="4"/>
+        <v>54</v>
+      </c>
+      <c r="B131" s="23">
+        <f t="shared" si="5"/>
         <v>3868</v>
       </c>
-      <c r="C131" s="35">
-        <f t="shared" si="4"/>
+      <c r="C131" s="25">
+        <f t="shared" si="5"/>
         <v>3853.2916666666665</v>
       </c>
-      <c r="D131" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E131" s="36"/>
-      <c r="F131" s="36"/>
-      <c r="G131" s="36"/>
+      <c r="D131" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E131" s="26"/>
+      <c r="F131" s="26"/>
+      <c r="G131" s="26"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B132" s="33">
-        <f t="shared" si="4"/>
+        <v>55</v>
+      </c>
+      <c r="B132" s="23">
+        <f t="shared" si="5"/>
         <v>4098</v>
       </c>
-      <c r="C132" s="35">
-        <f t="shared" si="4"/>
+      <c r="C132" s="25">
+        <f t="shared" si="5"/>
         <v>3875.5</v>
       </c>
-      <c r="D132" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E132" s="36"/>
-      <c r="F132" s="36"/>
-      <c r="G132" s="36"/>
+      <c r="D132" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E132" s="26"/>
+      <c r="F132" s="26"/>
+      <c r="G132" s="26"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B133" s="33">
-        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="B133" s="23">
+        <f t="shared" si="5"/>
         <v>4107</v>
       </c>
-      <c r="C133" s="35">
-        <f t="shared" si="4"/>
+      <c r="C133" s="25">
+        <f t="shared" si="5"/>
         <v>3899.8333333333335</v>
       </c>
-      <c r="D133" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E133" s="36"/>
-      <c r="F133" s="36"/>
-      <c r="G133" s="36"/>
+      <c r="D133" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E133" s="26"/>
+      <c r="F133" s="26"/>
+      <c r="G133" s="26"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B134" s="33">
-        <f t="shared" si="4"/>
+        <v>57</v>
+      </c>
+      <c r="B134" s="23">
+        <f t="shared" si="5"/>
         <v>4240</v>
       </c>
-      <c r="C134" s="33" t="str">
-        <f t="shared" si="4"/>
+      <c r="C134" s="23" t="str">
+        <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="D134" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E134" s="36"/>
-      <c r="F134" s="36"/>
-      <c r="G134" s="36"/>
+      <c r="D134" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E134" s="26"/>
+      <c r="F134" s="26"/>
+      <c r="G134" s="26"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B135" s="33">
-        <f t="shared" si="4"/>
+        <v>58</v>
+      </c>
+      <c r="B135" s="23">
+        <f t="shared" si="5"/>
         <v>4320</v>
       </c>
-      <c r="C135" s="33" t="str">
-        <f t="shared" si="4"/>
+      <c r="C135" s="23" t="str">
+        <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="D135" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E135" s="36"/>
-      <c r="F135" s="36"/>
-      <c r="G135" s="36"/>
+      <c r="D135" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E135" s="26"/>
+      <c r="F135" s="26"/>
+      <c r="G135" s="26"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B136" s="33">
-        <f t="shared" si="4"/>
+        <v>59</v>
+      </c>
+      <c r="B136" s="23">
+        <f t="shared" si="5"/>
         <v>4276</v>
       </c>
-      <c r="C136" s="33" t="str">
-        <f t="shared" si="4"/>
+      <c r="C136" s="23" t="str">
+        <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="D136" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E136" s="36"/>
-      <c r="F136" s="36"/>
-      <c r="G136" s="36"/>
+      <c r="D136" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E136" s="26"/>
+      <c r="F136" s="26"/>
+      <c r="G136" s="26"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B137" s="33">
-        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="B137" s="23">
+        <f t="shared" si="5"/>
         <v>4482</v>
       </c>
-      <c r="C137" s="33" t="str">
-        <f t="shared" si="4"/>
+      <c r="C137" s="23" t="str">
+        <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="D137" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E137" s="36"/>
-      <c r="F137" s="36"/>
-      <c r="G137" s="36"/>
+      <c r="D137" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E137" s="26"/>
+      <c r="F137" s="26"/>
+      <c r="G137" s="26"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B138" s="33">
-        <f t="shared" si="4"/>
+        <v>61</v>
+      </c>
+      <c r="B138" s="23">
+        <f t="shared" si="5"/>
         <v>3977</v>
       </c>
-      <c r="C138" s="33" t="str">
-        <f t="shared" si="4"/>
+      <c r="C138" s="23" t="str">
+        <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="D138" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E138" s="36"/>
-      <c r="F138" s="36"/>
-      <c r="G138" s="36"/>
+      <c r="D138" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E138" s="26"/>
+      <c r="F138" s="26"/>
+      <c r="G138" s="26"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B139" s="38">
-        <f t="shared" si="4"/>
+        <v>62</v>
+      </c>
+      <c r="B139" s="28">
+        <f t="shared" si="5"/>
         <v>3914</v>
       </c>
-      <c r="C139" s="38" t="str">
-        <f t="shared" si="4"/>
+      <c r="C139" s="28" t="str">
+        <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="D139" s="39">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E139" s="36"/>
-      <c r="F139" s="36"/>
-      <c r="G139" s="36"/>
+      <c r="D139" s="26" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E139" s="26"/>
+      <c r="F139" s="26"/>
+      <c r="G139" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5995,12 +6127,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6199,17 +6330,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E1B631-90B0-4D19-A35E-F8DC8BE167A4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a"/>
+    <ds:schemaRef ds:uri="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6234,18 +6375,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E1B631-90B0-4D19-A35E-F8DC8BE167A4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a"/>
-    <ds:schemaRef ds:uri="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/handouts/chapter_1_4_handout.xlsx
+++ b/handouts/chapter_1_4_handout.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\craigaj\Documents\GitHub\timeseries\handouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB479EB8-EC4C-47F2-BBD2-04049E53E882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0925D525-C348-4DBE-BB3F-D1A4D17F564A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11055" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
+    <workbookView xWindow="-5820" yWindow="-13110" windowWidth="19200" windowHeight="11175" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
   </bookViews>
   <sheets>
     <sheet name="Workbook" sheetId="2" r:id="rId1"/>
@@ -582,7 +582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -678,6 +678,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2149,7 +2158,7 @@
                       <m:accPr>
                         <m:chr m:val="̅"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -2322,7 +2331,7 @@
                     <m:accPr>
                       <m:chr m:val="̿"/>
                       <m:ctrlPr>
-                        <a:rPr lang="en-US" sz="1400" i="1">
+                        <a:rPr lang="en-US" sz="1400" b="0" i="1">
                           <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         </a:rPr>
                       </m:ctrlPr>
@@ -2451,8 +2460,8 @@
       <xdr:rowOff>77470</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="320040" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="18" name="TextBox 17">
@@ -2531,7 +2540,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="18" name="TextBox 17">
@@ -3313,8 +3322,8 @@
       <xdr:rowOff>210586</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="320040" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="TextBox 8">
@@ -3393,7 +3402,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="TextBox 8">
@@ -3893,7 +3902,6 @@
         <v>3351.5833333333335</v>
       </c>
       <c r="D9" s="27">
-        <f>IFERROR(B9-C9, "NA")</f>
         <v>378.41666666666652</v>
       </c>
     </row>
@@ -3907,7 +3915,9 @@
       <c r="C10" s="25">
         <v>3350</v>
       </c>
-      <c r="D10" s="26"/>
+      <c r="D10" s="27">
+        <v>59</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
@@ -3919,7 +3929,9 @@
       <c r="C11" s="25">
         <v>3343.2083333333335</v>
       </c>
-      <c r="D11" s="26"/>
+      <c r="D11" s="27">
+        <v>228.79166666666652</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
@@ -3931,7 +3943,9 @@
       <c r="C12" s="25">
         <v>3326.2083333333335</v>
       </c>
-      <c r="D12" s="26"/>
+      <c r="D12" s="27">
+        <v>302.79166666666652</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
@@ -3943,7 +3957,9 @@
       <c r="C13" s="25">
         <v>3316.5416666666665</v>
       </c>
-      <c r="D13" s="26"/>
+      <c r="D13" s="27">
+        <v>91.458333333333485</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
@@ -3955,7 +3971,9 @@
       <c r="C14" s="25">
         <v>3318.5833333333335</v>
       </c>
-      <c r="D14" s="26"/>
+      <c r="D14" s="27">
+        <v>72.416666666666515</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
@@ -4871,25 +4889,29 @@
         <v>3034</v>
       </c>
       <c r="C80" s="23" t="str">
-        <f t="shared" ref="C80:D80" si="0">C3</f>
+        <f t="shared" ref="C80" si="0">C3</f>
         <v>NA</v>
       </c>
-      <c r="D80" s="24" t="str">
+      <c r="D80" s="42" t="str">
         <f>IF(LEN(D3)&gt;0,D3,"")</f>
         <v>NA</v>
       </c>
-      <c r="E80" s="26"/>
+      <c r="E80" s="40">
+        <v>-345.22309027777783</v>
+      </c>
       <c r="F80" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="G80" s="26"/>
+      <c r="G80" s="41">
+        <v>3379.2230902777778</v>
+      </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B81" s="23">
-        <f t="shared" ref="B81:D96" si="1">B4</f>
+        <f t="shared" ref="B81:C96" si="1">B4</f>
         <v>2748</v>
       </c>
       <c r="C81" s="23" t="str">
@@ -5011,7 +5033,9 @@
         <v>378.41666666666652</v>
       </c>
       <c r="E86" s="26"/>
-      <c r="F86" s="26"/>
+      <c r="F86" s="25">
+        <v>11.473090277777715</v>
+      </c>
       <c r="G86" s="26"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.35">
@@ -5026,9 +5050,9 @@
         <f t="shared" si="1"/>
         <v>3350</v>
       </c>
-      <c r="D87" s="26" t="str">
+      <c r="D87" s="27">
         <f t="shared" si="2"/>
-        <v/>
+        <v>59</v>
       </c>
       <c r="E87" s="26"/>
       <c r="F87" s="26"/>
@@ -5046,9 +5070,9 @@
         <f t="shared" si="1"/>
         <v>3343.2083333333335</v>
       </c>
-      <c r="D88" s="26" t="str">
+      <c r="D88" s="27">
         <f t="shared" si="2"/>
-        <v/>
+        <v>228.79166666666652</v>
       </c>
       <c r="E88" s="26"/>
       <c r="F88" s="26"/>
@@ -5066,9 +5090,9 @@
         <f t="shared" si="1"/>
         <v>3326.2083333333335</v>
       </c>
-      <c r="D89" s="26" t="str">
+      <c r="D89" s="27">
         <f t="shared" si="2"/>
-        <v/>
+        <v>302.79166666666652</v>
       </c>
       <c r="E89" s="26"/>
       <c r="F89" s="26"/>
@@ -5086,9 +5110,9 @@
         <f t="shared" si="1"/>
         <v>3316.5416666666665</v>
       </c>
-      <c r="D90" s="26" t="str">
+      <c r="D90" s="27">
         <f t="shared" si="2"/>
-        <v/>
+        <v>91.458333333333485</v>
       </c>
       <c r="E90" s="26"/>
       <c r="F90" s="26"/>
@@ -5106,9 +5130,9 @@
         <f t="shared" si="1"/>
         <v>3318.5833333333335</v>
       </c>
-      <c r="D91" s="26" t="str">
+      <c r="D91" s="27">
         <f t="shared" si="2"/>
-        <v/>
+        <v>72.416666666666515</v>
       </c>
       <c r="E91" s="26"/>
       <c r="F91" s="26"/>
@@ -5220,7 +5244,7 @@
         <v>20</v>
       </c>
       <c r="B97" s="23">
-        <f t="shared" ref="B97:D112" si="3">B20</f>
+        <f t="shared" ref="B97:C112" si="3">B20</f>
         <v>3514</v>
       </c>
       <c r="C97" s="25">
@@ -5564,7 +5588,7 @@
         <v>36</v>
       </c>
       <c r="B113" s="23">
-        <f t="shared" ref="B113:D128" si="4">B36</f>
+        <f t="shared" ref="B113:C128" si="4">B36</f>
         <v>3506</v>
       </c>
       <c r="C113" s="25">
@@ -5897,7 +5921,7 @@
         <v>52</v>
       </c>
       <c r="B129" s="23">
-        <f t="shared" ref="B129:D139" si="5">B52</f>
+        <f t="shared" ref="B129:C139" si="5">B52</f>
         <v>2792</v>
       </c>
       <c r="C129" s="25">
@@ -6127,6 +6151,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_activity xmlns="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xsi:nil="true"/>
@@ -6134,7 +6167,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010070F75838E79B0E48B83E8E3F5479A3A2" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2b0c304636f8f537543cd13f583db9d4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xmlns:ns4="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0f089f22c5ce4e61126931f7622145b2" ns3:_="" ns4:_="">
     <xsd:import namespace="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
@@ -6329,16 +6362,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E1B631-90B0-4D19-A35E-F8DC8BE167A4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -6355,7 +6387,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBDDC771-C014-4A48-9FCA-802C556EA1D0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6372,12 +6404,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>